--- a/datos/VENTAS_Y_ABONOS_VU.xlsx
+++ b/datos/VENTAS_Y_ABONOS_VU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91172C5B-65BF-4A1B-95DE-CC87E6938F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60FFE37C-983F-4AB6-8D8A-ADA9E3D201D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,54 +20,1461 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="658">
+  <si>
+    <t>EMPRESA</t>
+  </si>
+  <si>
+    <t>CONTRATO</t>
+  </si>
+  <si>
+    <t>PIE_COMPLETO</t>
+  </si>
+  <si>
+    <t>MONTO_ABONADO</t>
+  </si>
+  <si>
+    <t>DISTRITO</t>
+  </si>
+  <si>
+    <t>GERENTE_DISTRITO</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>FECHA_CONTRATO</t>
+  </si>
   <si>
     <t>CLIENTE</t>
   </si>
   <si>
-    <t>TIPO_CONTRATO</t>
-  </si>
-  <si>
-    <t>CONTRATO</t>
-  </si>
-  <si>
-    <t>IMPORTE_CONTRATO</t>
-  </si>
-  <si>
-    <t>ANTICIPO</t>
-  </si>
-  <si>
-    <t>SALDO_FINANCIAR</t>
+    <t>RUT</t>
+  </si>
+  <si>
+    <t>DOMICILIO</t>
+  </si>
+  <si>
+    <t>REGION</t>
+  </si>
+  <si>
+    <t>LOCALIDAD</t>
+  </si>
+  <si>
+    <t>COMUNA</t>
+  </si>
+  <si>
+    <t>TELEFONO_1</t>
+  </si>
+  <si>
+    <t>TELEFONO_2</t>
+  </si>
+  <si>
+    <t>EMAIL</t>
+  </si>
+  <si>
+    <t>TIPO_DE_SERVICIO</t>
+  </si>
+  <si>
+    <t>PROGRAMA</t>
+  </si>
+  <si>
+    <t>CATEGORIA</t>
+  </si>
+  <si>
+    <t>MONEDA</t>
+  </si>
+  <si>
+    <t>PRECIO_LISTA</t>
+  </si>
+  <si>
+    <t>PIE</t>
+  </si>
+  <si>
+    <t>PORC_PIE</t>
+  </si>
+  <si>
+    <t>DESCUENTO</t>
+  </si>
+  <si>
+    <t>PORC_DESCUENTO</t>
+  </si>
+  <si>
+    <t>PRECIO_VENTA</t>
+  </si>
+  <si>
+    <t>TOTAL_VENTA_SIN_IVA</t>
+  </si>
+  <si>
+    <t>SALDO</t>
+  </si>
+  <si>
+    <t>MEDIO_PAGO</t>
   </si>
   <si>
     <t>CANT_CUOTAS</t>
   </si>
   <si>
-    <t>ANTICIPO_PIE</t>
-  </si>
-  <si>
-    <t>LIDER</t>
-  </si>
-  <si>
-    <t>VENDEDOR</t>
-  </si>
-  <si>
-    <t>CONDICION_VENTA</t>
-  </si>
-  <si>
-    <t>SALDO</t>
+    <t>MONTO_CUOTA</t>
+  </si>
+  <si>
+    <t>DIA_PAGO</t>
+  </si>
+  <si>
+    <t>PRIMER_VENCIMIENTO_TXT</t>
+  </si>
+  <si>
+    <t>CAPACIDAD</t>
+  </si>
+  <si>
+    <t>PARCELA</t>
+  </si>
+  <si>
+    <t>MANZANA</t>
+  </si>
+  <si>
+    <t>MIN_FECHA_SALDO</t>
+  </si>
+  <si>
+    <t>VALLES UNIDOS S.A.</t>
+  </si>
+  <si>
+    <t>1015732</t>
+  </si>
+  <si>
+    <t>COMPLETADO</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>GERENCIA NECESIDAD FUTURA TERRENO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Camilo Jesus Medel Rojas</t>
+  </si>
+  <si>
+    <t>Rodrigo Ignacio Castro Figueroa</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>PEÑALOZA SANDOVAL ELBA ANGELA</t>
+  </si>
+  <si>
+    <t>8045408-2</t>
+  </si>
+  <si>
+    <t>Av. las torres poniente, ALT 559 - Quilicura -</t>
+  </si>
+  <si>
+    <t>Metropolitana</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>Quilicura</t>
+  </si>
+  <si>
+    <t>984167803</t>
+  </si>
+  <si>
+    <t>penaloza.elbas59@gmai.com</t>
+  </si>
+  <si>
+    <t>Mantención Perpetua Simple</t>
+  </si>
+  <si>
+    <t>PESOS</t>
+  </si>
+  <si>
+    <t>4600000</t>
+  </si>
+  <si>
+    <t>3220000</t>
+  </si>
+  <si>
+    <t>0.7</t>
+  </si>
+  <si>
+    <t>1380000</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>2705882.35</t>
+  </si>
+  <si>
+    <t>OFICINA</t>
+  </si>
+  <si>
+    <t>1015659</t>
+  </si>
+  <si>
+    <t>Estefany francisca gonzalez morales</t>
+  </si>
+  <si>
+    <t>YASMELY RAMONA VARGAS INFANTE</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>CORTES CORTES RENE ORLANDO</t>
+  </si>
+  <si>
+    <t>7655592-3</t>
+  </si>
+  <si>
+    <t>Pasaje volcan lonquimay, ALT 388 - Quilicura -</t>
+  </si>
+  <si>
+    <t>930741552</t>
+  </si>
+  <si>
+    <t>RENECORTES057@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>Mantención Perpetua Integral</t>
+  </si>
+  <si>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>300000</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>2521008.4</t>
+  </si>
+  <si>
+    <t>2700000</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>02/05/2026</t>
+  </si>
+  <si>
+    <t>1015661</t>
+  </si>
+  <si>
+    <t>RIVEROS GARIB ANDRES GERMAN</t>
+  </si>
+  <si>
+    <t>13463050-7</t>
+  </si>
+  <si>
+    <t>Los pirineos, ALT 371 - Quilicura -</t>
+  </si>
+  <si>
+    <t>984190676</t>
+  </si>
+  <si>
+    <t>jacseguridad2017@gmail.com</t>
+  </si>
+  <si>
+    <t>1015658</t>
+  </si>
+  <si>
+    <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
+  </si>
+  <si>
+    <t>Yohany Margarita Gonzalez Rojas</t>
+  </si>
+  <si>
+    <t>PEREIRA PEREZ YOLANDA</t>
+  </si>
+  <si>
+    <t>14644783-k</t>
+  </si>
+  <si>
+    <t>Pichasca, ALT 664 - Quilicura -</t>
+  </si>
+  <si>
+    <t>978460802</t>
+  </si>
+  <si>
+    <t>yolandapereirap@gmail.com</t>
+  </si>
+  <si>
+    <t>Mantención Perpetua Doble</t>
+  </si>
+  <si>
+    <t>6300000</t>
+  </si>
+  <si>
+    <t>535500</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>945000</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>5355000</t>
+  </si>
+  <si>
+    <t>4500000</t>
+  </si>
+  <si>
+    <t>4819500</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>100418</t>
+  </si>
+  <si>
+    <t>1015657</t>
+  </si>
+  <si>
+    <t>Margarita Cristina Rojas Quezada</t>
+  </si>
+  <si>
+    <t>VENEGAS SEPULVEDA ALEXANDRA NATALIE</t>
+  </si>
+  <si>
+    <t>20327901-9</t>
+  </si>
+  <si>
+    <t>Filomena garate 740, Quilicura, Santiago, Metropolitana  Pi/dp U 25 Casa:</t>
+  </si>
+  <si>
+    <t>959186333</t>
+  </si>
+  <si>
+    <t>alexandra.natalie.vs@gmail.com</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>05/04/2026</t>
+  </si>
+  <si>
+    <t>1015611</t>
+  </si>
+  <si>
+    <t>Francesca Nicole Sanchez pacheco</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>AYALA VILLARROEL NORMA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>7563296-7</t>
+  </si>
+  <si>
+    <t>EL ALERCE 1093, VILLA SANTA TERESITA, QUILICURA, SANTIAGO  Casa: letra i</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>QUILICURA</t>
+  </si>
+  <si>
+    <t>VILLA SANTA TERESITA</t>
+  </si>
+  <si>
+    <t>962053244</t>
+  </si>
+  <si>
+    <t>normaayala982@gmail.com</t>
+  </si>
+  <si>
+    <t>56250</t>
+  </si>
+  <si>
+    <t>1015720</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>GAETE OSORIO MARINA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>10068490-K</t>
+  </si>
+  <si>
+    <t>Rio choapa, ALT 767 - Quilicura -</t>
+  </si>
+  <si>
+    <t>988987431</t>
+  </si>
+  <si>
+    <t>marna.gaete01@gmail.com</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>45746</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>2026-04-01T00:00:00</t>
+  </si>
+  <si>
+    <t>1015676</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>ARANCIBIA GAMBOA ROBERTO JAIME</t>
+  </si>
+  <si>
+    <t>4137131-5</t>
+  </si>
+  <si>
+    <t>mafil  6132, Pedro Aguirre Cerda, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t>936398005 - 91368496</t>
+  </si>
+  <si>
+    <t>rarancibia430@gmail.com</t>
+  </si>
+  <si>
+    <t>1015708</t>
+  </si>
+  <si>
+    <t>VEGA ITURRIETA MARIA MARGARITA</t>
+  </si>
+  <si>
+    <t>10758714-4</t>
+  </si>
+  <si>
+    <t>Jorge Luis Borges, ALT 158 - Quilicura -</t>
+  </si>
+  <si>
+    <t>954111244</t>
+  </si>
+  <si>
+    <t>MMVEGA71@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>1015600</t>
+  </si>
+  <si>
+    <t>28/02/2026</t>
+  </si>
+  <si>
+    <t>COLIL QUINTREQUEO ANA MARIA</t>
+  </si>
+  <si>
+    <t>9896466-5</t>
+  </si>
+  <si>
+    <t>Filomena garate 1050, Quilicura, Santiago, Metropolitana  Pi/dp 102 Casa:</t>
+  </si>
+  <si>
+    <t>935664891</t>
+  </si>
+  <si>
+    <t>TANIA.CEBALLOS.MOYA78@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>15/04/2026</t>
+  </si>
+  <si>
+    <t>1015601</t>
+  </si>
+  <si>
+    <t>1030.09</t>
+  </si>
+  <si>
+    <t>Marcela Antonia  Valdés  Barrios</t>
+  </si>
+  <si>
+    <t>LETELIER RUZ ELOISA DE LAS MERCEDES</t>
+  </si>
+  <si>
+    <t>9764810-7</t>
+  </si>
+  <si>
+    <t>Pje bombero sergio larenas 380, Quilicura, Santiago, Metropolitana  Pi/dp 313 Casa:</t>
+  </si>
+  <si>
+    <t>965810449</t>
+  </si>
+  <si>
+    <t>222447778</t>
+  </si>
+  <si>
+    <t>eloisaletelier147@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-02-25T00:00:00</t>
+  </si>
+  <si>
+    <t>1015604</t>
+  </si>
+  <si>
+    <t>TOMAS IGNACIO PROVOSTE NAVARRETE</t>
+  </si>
+  <si>
+    <t>RAMIREZ ROJAS GLORIA ELIZABETH</t>
+  </si>
+  <si>
+    <t>12259550-1</t>
+  </si>
+  <si>
+    <t>Chacabuco El Mañio 630, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>953408712 - 56953408712</t>
+  </si>
+  <si>
+    <t>gloria.gr@gmail.com</t>
+  </si>
+  <si>
+    <t>1500000</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>690000</t>
+  </si>
+  <si>
+    <t>3910000</t>
+  </si>
+  <si>
+    <t>3285714.29</t>
+  </si>
+  <si>
+    <t>2410000</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>133887</t>
+  </si>
+  <si>
+    <t>1015719</t>
+  </si>
+  <si>
+    <t>ANDREA VALESKA SAFFA ROMERO</t>
+  </si>
+  <si>
+    <t>CARRASCO HERNANDEZ MARTA</t>
+  </si>
+  <si>
+    <t>8626435-8</t>
+  </si>
+  <si>
+    <t>Pasaje pullay, ALT 5838 - Renca -</t>
+  </si>
+  <si>
+    <t>Renca</t>
+  </si>
+  <si>
+    <t>954940199</t>
+  </si>
+  <si>
+    <t>936883029</t>
+  </si>
+  <si>
+    <t>jessica.carrasco46@gmail.com</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>1015722</t>
+  </si>
+  <si>
+    <t>260000</t>
+  </si>
+  <si>
+    <t>CAYUN COÑOMAN ELIZARDO FREDDY</t>
+  </si>
+  <si>
+    <t>11039322-9</t>
+  </si>
+  <si>
+    <t>Pullay 5838 5838, Renca, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>936883092</t>
+  </si>
+  <si>
+    <t>936883092 - 95899950</t>
+  </si>
+  <si>
+    <t>jessicaz.carrasco45@gmail.com</t>
+  </si>
+  <si>
+    <t>1015724</t>
+  </si>
+  <si>
+    <t>Veronica cecilia gonzalez morales</t>
+  </si>
+  <si>
+    <t>FUENTES ARAYA BEATRIZ DE LAS MERCEDEZ</t>
+  </si>
+  <si>
+    <t>8431496-k</t>
+  </si>
+  <si>
+    <t>CALLE 1, BLOCK 1 1304, Colina, Chacabuco, Metropolitana  Pi/dp 104 Casa:</t>
+  </si>
+  <si>
+    <t>Chacabuco</t>
+  </si>
+  <si>
+    <t>Colina</t>
+  </si>
+  <si>
+    <t>966723315</t>
+  </si>
+  <si>
+    <t>966723315 - 56966723315</t>
+  </si>
+  <si>
+    <t>beatrizfuentesaraya@gmail.com</t>
+  </si>
+  <si>
+    <t>1015734</t>
+  </si>
+  <si>
+    <t>GÓMEZ URQUIOLA GABRIEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>14355767-7</t>
+  </si>
+  <si>
+    <t>Pasaje moay , ALT 1919 - Lampa -</t>
+  </si>
+  <si>
+    <t>Lampa</t>
+  </si>
+  <si>
+    <t>934465509 - 56934465509</t>
+  </si>
+  <si>
+    <t>gomezurquiola@gmail.com</t>
+  </si>
+  <si>
+    <t>414000</t>
+  </si>
+  <si>
+    <t>460000</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>4140000</t>
+  </si>
+  <si>
+    <t>3478991.6</t>
+  </si>
+  <si>
+    <t>3726000</t>
+  </si>
+  <si>
+    <t>103500</t>
+  </si>
+  <si>
+    <t>1015617</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>GUAJARDO VERGARA AURORA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>10816341-0</t>
+  </si>
+  <si>
+    <t>LAMPA</t>
+  </si>
+  <si>
+    <t>967304045</t>
+  </si>
+  <si>
+    <t>florcita66guajardo@gmail.com</t>
+  </si>
+  <si>
+    <t>77625</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>1015616</t>
+  </si>
+  <si>
+    <t>LOPEZ CERDA GLORIA ANGELICA</t>
+  </si>
+  <si>
+    <t>8429029-7</t>
+  </si>
+  <si>
+    <t>Quinquila 1323, ALT 1323 - Lampa -</t>
+  </si>
+  <si>
+    <t>986729324</t>
+  </si>
+  <si>
+    <t>DIEGORLANDO.LOPEZ2121@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>225000</t>
+  </si>
+  <si>
+    <t>1015683</t>
+  </si>
+  <si>
+    <t>Nayaret Tatiana Puga Marchant</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>HERMOSILLA NORAMBUENA GRACIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>6839198-9</t>
+  </si>
+  <si>
+    <t>La exótica  11122, La Pintana, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>La Pintana</t>
+  </si>
+  <si>
+    <t>987418795</t>
+  </si>
+  <si>
+    <t>mana2010@live.cl</t>
+  </si>
+  <si>
+    <t>1000000</t>
+  </si>
+  <si>
+    <t>2000000</t>
+  </si>
+  <si>
+    <t>33916</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>1015622</t>
+  </si>
+  <si>
+    <t>MARIA CLARISA ARRAÑO MORALES</t>
+  </si>
+  <si>
+    <t>ESPINOZA GALAZ BERNARDO JACINTO</t>
+  </si>
+  <si>
+    <t>9355678-k</t>
+  </si>
+  <si>
+    <t>Estero ablemo 74, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>996712506 - 56996712506</t>
+  </si>
+  <si>
+    <t>espinozabernardo1@gmail.com</t>
+  </si>
+  <si>
+    <t>3680000</t>
+  </si>
+  <si>
+    <t>76651</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>22/04/2026</t>
+  </si>
+  <si>
+    <t>1015684</t>
+  </si>
+  <si>
+    <t>GUERRA LEIVA ANA EDELMIRA</t>
+  </si>
+  <si>
+    <t>11399404-3</t>
+  </si>
+  <si>
+    <t>Pampa del tamarugal, ALT 456 - Quilicura -</t>
+  </si>
+  <si>
+    <t>957359715</t>
+  </si>
+  <si>
+    <t>942854716</t>
+  </si>
+  <si>
+    <t>edelmiraguerraleiv@gmail.com - EDELMIRAGUERRALEIV@</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>24/04/2026</t>
+  </si>
+  <si>
+    <t>1015632</t>
+  </si>
+  <si>
+    <t>Fernanda Scarlet Cuevas Olivares</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>MENDOZA ORDENES ENNA ELIZABETH</t>
+  </si>
+  <si>
+    <t>10033214-0</t>
+  </si>
+  <si>
+    <t>NUESTRA SEÑORA DEL CARMEN 534 24, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>949464419</t>
+  </si>
+  <si>
+    <t>950009831</t>
+  </si>
+  <si>
+    <t>KATHERINSOTOGARRIDO@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>25/04/2026</t>
+  </si>
+  <si>
+    <t>1015652</t>
+  </si>
+  <si>
+    <t>787410</t>
+  </si>
+  <si>
+    <t>Betzabeth nicole chacon quinteros</t>
+  </si>
+  <si>
+    <t>MENESES ZUÑIGA MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>9583970-3</t>
+  </si>
+  <si>
+    <t>av marcoleta, ALT 1580 - Quilicura -</t>
+  </si>
+  <si>
+    <t>966830329</t>
+  </si>
+  <si>
+    <t>marcomeneses684@gmail.com</t>
+  </si>
+  <si>
+    <t>630000</t>
+  </si>
+  <si>
+    <t>410000</t>
+  </si>
+  <si>
+    <t>6.51</t>
+  </si>
+  <si>
+    <t>5890000</t>
+  </si>
+  <si>
+    <t>4949579.83</t>
+  </si>
+  <si>
+    <t>5260000</t>
+  </si>
+  <si>
+    <t>146115</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>2025-11-16T00:00:00</t>
+  </si>
+  <si>
+    <t>1015714</t>
+  </si>
+  <si>
+    <t>VIVIANA HERNANDEZ</t>
+  </si>
+  <si>
+    <t>XIMENA DEL CARMEN LOPEZ ROZAS</t>
+  </si>
+  <si>
+    <t>CID VALDEBENITO JOSÉ ADRIAN</t>
+  </si>
+  <si>
+    <t>7635948-2</t>
+  </si>
+  <si>
+    <t>San Luis 250 12, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>968786800 - 56968786800</t>
+  </si>
+  <si>
+    <t>cidjose547@gmail.com</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>1015701</t>
+  </si>
+  <si>
+    <t>ZAMORA MORENO JOSÉ TOMAS</t>
+  </si>
+  <si>
+    <t>8037977-3</t>
+  </si>
+  <si>
+    <t>Pasaje rebodello, ALT 548 - Quilicura -</t>
+  </si>
+  <si>
+    <t>981588402</t>
+  </si>
+  <si>
+    <t>josezamorac.60@gmail.com</t>
+  </si>
+  <si>
+    <t>1015733</t>
+  </si>
+  <si>
+    <t>KATHERINE ANDREA ROMERO MILLAN</t>
+  </si>
+  <si>
+    <t>RIOS ITURRA MARIO HUMBERTO</t>
+  </si>
+  <si>
+    <t>7192742-3</t>
+  </si>
+  <si>
+    <t>Coquimbo, ALT 890 - San Antonio -</t>
+  </si>
+  <si>
+    <t>Valparaíso</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>987209124</t>
+  </si>
+  <si>
+    <t>proferios@hotmail.com</t>
+  </si>
+  <si>
+    <t>3865546.22</t>
+  </si>
+  <si>
+    <t>172500</t>
+  </si>
+  <si>
+    <t>1015641</t>
+  </si>
+  <si>
+    <t>ABONADO</t>
+  </si>
+  <si>
+    <t>daniela castro valdebenito</t>
+  </si>
+  <si>
+    <t>VENEGAS ASTORGA IRIS DEL CARMEN</t>
+  </si>
+  <si>
+    <t>11739202-3</t>
+  </si>
+  <si>
+    <t>Los espinos , ALT 138 - Lampa -</t>
+  </si>
+  <si>
+    <t>931276144 - 56931276144</t>
+  </si>
+  <si>
+    <t>irisvenegas260@gmail.com - IRISVENEGAS260@GMAIL.CO</t>
+  </si>
+  <si>
+    <t>155250</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>2026-02-12T00:00:00</t>
+  </si>
+  <si>
+    <t>1015662</t>
+  </si>
+  <si>
+    <t>Planes Parque</t>
+  </si>
+  <si>
+    <t>Valle Del Descanso (cuotas)</t>
+  </si>
+  <si>
+    <t>Valle Del Descanso</t>
+  </si>
+  <si>
+    <t>3450000</t>
+  </si>
+  <si>
+    <t>400000</t>
+  </si>
+  <si>
+    <t>0.12</t>
+  </si>
+  <si>
+    <t>3050000</t>
+  </si>
+  <si>
+    <t>84730</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>SIN ASIGNAR</t>
+  </si>
+  <si>
+    <t>MIGRAR</t>
+  </si>
+  <si>
+    <t>1015663</t>
+  </si>
+  <si>
+    <t>CATALINA PATRICIA CABRERA HORMAZABAL</t>
+  </si>
+  <si>
+    <t>LEON JIMENEZ BYRON ANDRES</t>
+  </si>
+  <si>
+    <t>20329081-0</t>
+  </si>
+  <si>
+    <t>Manuel antonio matta 0595, ALT 595 - Quilicura -</t>
+  </si>
+  <si>
+    <t>935435179</t>
+  </si>
+  <si>
+    <t>BYRONLYON1999@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>Valle De La Memoria (cuotas)</t>
+  </si>
+  <si>
+    <t>Valle De La Memoria</t>
+  </si>
+  <si>
+    <t>4990000</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>998000</t>
+  </si>
+  <si>
+    <t>3992000</t>
+  </si>
+  <si>
+    <t>3592000</t>
+  </si>
+  <si>
+    <t>99770</t>
+  </si>
+  <si>
+    <t>1015633</t>
+  </si>
+  <si>
+    <t>ALEJANDRA VERDUGO</t>
+  </si>
+  <si>
+    <t>LEYTON CORVALAN BELEN ANDREA</t>
+  </si>
+  <si>
+    <t>21597118-k</t>
+  </si>
+  <si>
+    <t>Pasaje coral de año nuevo, ALT 513 - La Granja -</t>
+  </si>
+  <si>
+    <t>La Granja</t>
+  </si>
+  <si>
+    <t>994206017</t>
+  </si>
+  <si>
+    <t>bleytoncorvalan957@gmail.com</t>
+  </si>
+  <si>
+    <t>Valle De Las Rosas (cuotas)</t>
+  </si>
+  <si>
+    <t>Valle De Las Rosas</t>
+  </si>
+  <si>
+    <t>5880000</t>
+  </si>
+  <si>
+    <t>588000</t>
+  </si>
+  <si>
+    <t>5292000</t>
+  </si>
+  <si>
+    <t>147000</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>1015631</t>
+  </si>
+  <si>
+    <t>NF CARTERA</t>
+  </si>
+  <si>
+    <t>CAYUN HEREDIA KAREN ANDREA</t>
+  </si>
+  <si>
+    <t>18190149-7</t>
+  </si>
+  <si>
+    <t>pasaje  estacion loncoche, ALT 228 - Huechuraba -</t>
+  </si>
+  <si>
+    <t>Huechuraba</t>
+  </si>
+  <si>
+    <t>920512919</t>
+  </si>
+  <si>
+    <t>920234538</t>
+  </si>
+  <si>
+    <t>KARENCAYUNHEREDIA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>4533000</t>
+  </si>
+  <si>
+    <t>77.09</t>
+  </si>
+  <si>
+    <t>1347000</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>1015606</t>
+  </si>
+  <si>
+    <t>MADRID GAETE NICXA VIVIANA</t>
+  </si>
+  <si>
+    <t>19586921-9</t>
+  </si>
+  <si>
+    <t>Psje jose carreno trujillo, ALT 1675 - Lampa -</t>
+  </si>
+  <si>
+    <t>935565885</t>
+  </si>
+  <si>
+    <t>nixa@gmail.com</t>
+  </si>
+  <si>
+    <t>59847</t>
+  </si>
+  <si>
+    <t>1015736</t>
+  </si>
+  <si>
+    <t>116.12</t>
+  </si>
+  <si>
+    <t>VARGAS CAMPOS LUIS MIGUEL</t>
+  </si>
+  <si>
+    <t>12003266-6</t>
+  </si>
+  <si>
+    <t>Blanco Encalada, ALT 144 - Quilicura -</t>
+  </si>
+  <si>
+    <t>931377299</t>
+  </si>
+  <si>
+    <t>LUISMIGUEL.VARGASC@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>450000</t>
+  </si>
+  <si>
+    <t>499000</t>
+  </si>
+  <si>
+    <t>4491000</t>
+  </si>
+  <si>
+    <t>4041000</t>
+  </si>
+  <si>
+    <t>112250</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>16/05/2026</t>
+  </si>
+  <si>
+    <t>2024-01-31T00:00:00</t>
+  </si>
+  <si>
+    <t>1015713</t>
+  </si>
+  <si>
+    <t>ERNESTO OLIVA</t>
+  </si>
+  <si>
+    <t>MIGUEL SANDOVAL</t>
+  </si>
+  <si>
+    <t>ANDREA CONCHA ADASME</t>
+  </si>
+  <si>
+    <t>SOTO LILLO RAMIRO HERNAN</t>
+  </si>
+  <si>
+    <t>8.944.333-4</t>
+  </si>
+  <si>
+    <t>Psje mincha, la foresta 1, ALT 730 - Quilicura -</t>
+  </si>
+  <si>
+    <t>983831323</t>
+  </si>
+  <si>
+    <t>marjorienicole.so@gmail.com</t>
+  </si>
+  <si>
+    <t>66553</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3-AI-21</t>
+  </si>
+  <si>
+    <t>Valle de la Memoria</t>
+  </si>
+  <si>
+    <t>1015685</t>
+  </si>
+  <si>
+    <t>130000</t>
+  </si>
+  <si>
+    <t>MILLAN LEVIO ELENA FRESIA</t>
+  </si>
+  <si>
+    <t>10483632-1</t>
+  </si>
+  <si>
+    <t>manuel busto 0451, ALT 451 - Quilicura -</t>
+  </si>
+  <si>
+    <t>937231044</t>
+  </si>
+  <si>
+    <t>elenamillanlevio64@gmail.com</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>49888.88</t>
+  </si>
+  <si>
+    <t>09/05/2026</t>
+  </si>
+  <si>
+    <t>3-AT-43</t>
+  </si>
+  <si>
+    <t>2025-10-31T00:00:00</t>
+  </si>
+  <si>
+    <t>1015629</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ ESPINOZA ALONSO</t>
+  </si>
+  <si>
+    <t>22318996-2</t>
+  </si>
+  <si>
+    <t>cienfuegos 5455, ALT 5455 - Pedro Aguirre Cerda -</t>
+  </si>
+  <si>
+    <t>978737691</t>
+  </si>
+  <si>
+    <t>alonsorodriguezespinoza1904@gmail.com</t>
+  </si>
+  <si>
+    <t>3990000</t>
+  </si>
+  <si>
+    <t>79.96</t>
+  </si>
+  <si>
+    <t>3-BA-43</t>
+  </si>
+  <si>
+    <t>1015717</t>
+  </si>
+  <si>
+    <t>445000</t>
+  </si>
+  <si>
+    <t>MILLA CASTRO HERNAN SERGIO</t>
+  </si>
+  <si>
+    <t>9003503-7</t>
+  </si>
+  <si>
+    <t>lo marcoleta 1620, ALT 1620 - ASENTAMIENTO COLO COLO -</t>
+  </si>
+  <si>
+    <t>ASENTAMIENTO COLO COLO</t>
+  </si>
+  <si>
+    <t>987779762</t>
+  </si>
+  <si>
+    <t>992530684</t>
+  </si>
+  <si>
+    <t>wally313@hotmail.com</t>
+  </si>
+  <si>
+    <t>4545000</t>
+  </si>
+  <si>
+    <t>91.08</t>
+  </si>
+  <si>
+    <t>3-I-29</t>
+  </si>
+  <si>
+    <t>2026-03-30T00:00:00</t>
+  </si>
+  <si>
+    <t>1015735</t>
+  </si>
+  <si>
+    <t>LIDIA MONICA FLORES BRAVO</t>
   </si>
   <si>
     <t>ROBLES CISTERNAS MARGARITA ALEJANDRA</t>
   </si>
   <si>
-    <t>Valle De La Memoria</t>
-  </si>
-  <si>
-    <t>1015731</t>
-  </si>
-  <si>
-    <t>4990000</t>
+    <t>12353329-1</t>
+  </si>
+  <si>
+    <t>El medio dia, ALT 358 - Quilicura -</t>
+  </si>
+  <si>
+    <t>994485350</t>
+  </si>
+  <si>
+    <t>robles.cisterm@gmail.com</t>
   </si>
   <si>
     <t>500000</t>
@@ -76,193 +1483,517 @@
     <t>4490000</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
-  </si>
-  <si>
-    <t>LIDIA MONICA FLORES BRAVO</t>
-  </si>
-  <si>
-    <t>CREDITO CTTOS</t>
-  </si>
-  <si>
-    <t>0</t>
+    <t>76084</t>
+  </si>
+  <si>
+    <t>3-V-21</t>
+  </si>
+  <si>
+    <t>1015718</t>
+  </si>
+  <si>
+    <t>ROSAS PALOMINOS MARISELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>20033453-1</t>
+  </si>
+  <si>
+    <t>Estadio nacional  87, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>994955673</t>
+  </si>
+  <si>
+    <t>rosasmarisela382@gmail.com</t>
+  </si>
+  <si>
+    <t>3991000</t>
+  </si>
+  <si>
+    <t>66497</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>4-F-39</t>
+  </si>
+  <si>
+    <t>Valle de la Memoria 2</t>
+  </si>
+  <si>
+    <t>1015721</t>
+  </si>
+  <si>
+    <t>LOPEZ RUZ ENRIQUE ANTONIO</t>
+  </si>
+  <si>
+    <t>17065070-0</t>
+  </si>
+  <si>
+    <t>manuel antonio matta, ALT 690 - Quilicura -</t>
+  </si>
+  <si>
+    <t>922145316</t>
+  </si>
+  <si>
+    <t>956637958</t>
+  </si>
+  <si>
+    <t>enriquelopezruz@gmail.com</t>
+  </si>
+  <si>
+    <t>74849</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>4-K-25</t>
+  </si>
+  <si>
+    <t>1015647</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>LLANCALEO ZAMORANO SILVANA VALENTINA</t>
+  </si>
+  <si>
+    <t>15957544-6</t>
+  </si>
+  <si>
+    <t>Av lo cruzat  525, Quilicura, Santiago, Metropolitana  Pi/dp 722 Casa:  Edificio 7</t>
+  </si>
+  <si>
+    <t>994481549</t>
+  </si>
+  <si>
+    <t>Silvll84@gmail.com</t>
+  </si>
+  <si>
+    <t>1300000</t>
+  </si>
+  <si>
+    <t>0.26</t>
+  </si>
+  <si>
+    <t>3191000</t>
+  </si>
+  <si>
+    <t>265913</t>
+  </si>
+  <si>
+    <t>4-Z-42</t>
+  </si>
+  <si>
+    <t>1015711</t>
+  </si>
+  <si>
+    <t>OLIVARES ACUÑA LORENA ALEXANDRA</t>
+  </si>
+  <si>
+    <t>18941442-0</t>
+  </si>
+  <si>
+    <t>Hualañe 300, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>946513572</t>
+  </si>
+  <si>
+    <t>lorenaalexandra656@gmail.com</t>
+  </si>
+  <si>
+    <t>Valle De La Paz (cuotas)</t>
+  </si>
+  <si>
+    <t>Valle De La Paz</t>
+  </si>
+  <si>
+    <t>4350000</t>
+  </si>
+  <si>
+    <t>397000</t>
+  </si>
+  <si>
+    <t>389000</t>
+  </si>
+  <si>
+    <t>8.94</t>
+  </si>
+  <si>
+    <t>3961000</t>
+  </si>
+  <si>
+    <t>3564000</t>
+  </si>
+  <si>
+    <t>99000</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>14/05/2026</t>
+  </si>
+  <si>
+    <t>5-Q-69</t>
+  </si>
+  <si>
+    <t>Valle de la Paz</t>
+  </si>
+  <si>
+    <t>1015730</t>
+  </si>
+  <si>
+    <t>6750</t>
+  </si>
+  <si>
+    <t>Micaela Tais Vargas Castillo</t>
   </si>
   <si>
     <t>ZÚÑIGA BAGINSKY ROBERTO</t>
   </si>
   <si>
-    <t>Valle Del Descanso</t>
-  </si>
-  <si>
-    <t>1015730</t>
+    <t>5233612-0</t>
+  </si>
+  <si>
+    <t>Esmeralda 824 block7, ALT 25 - Lo Prado -</t>
+  </si>
+  <si>
+    <t>Lo Prado</t>
+  </si>
+  <si>
+    <t>965951520</t>
+  </si>
+  <si>
+    <t>czuñigab44@gmail.com</t>
+  </si>
+  <si>
+    <t>293250</t>
+  </si>
+  <si>
+    <t>517500</t>
   </si>
   <si>
     <t>2932500</t>
   </si>
   <si>
-    <t>293250</t>
-  </si>
-  <si>
     <t>2639250</t>
   </si>
   <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>Camilo Jesus Medel Rojas</t>
-  </si>
-  <si>
-    <t>Micaela Tais Vargas Castillo</t>
-  </si>
-  <si>
-    <t>GÓMEZ URQUIOLA GABRIEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>Mantención Perpetua Simple</t>
-  </si>
-  <si>
-    <t>1015734</t>
-  </si>
-  <si>
-    <t>4140000</t>
-  </si>
-  <si>
-    <t>414000</t>
-  </si>
-  <si>
-    <t>3726000</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>Estefany francisca gonzalez morales</t>
-  </si>
-  <si>
-    <t>Veronica cecilia gonzalez morales</t>
-  </si>
-  <si>
-    <t>CREDITO CTTOS MP</t>
-  </si>
-  <si>
-    <t>CAYUN COÑOMAN ELIZARDO FREDDY</t>
-  </si>
-  <si>
-    <t>Mantención Perpetua Integral</t>
-  </si>
-  <si>
-    <t>1015722</t>
-  </si>
-  <si>
-    <t>3000000</t>
-  </si>
-  <si>
-    <t>300000</t>
-  </si>
-  <si>
-    <t>2700000</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Rodrigo Ignacio Castro Figueroa</t>
-  </si>
-  <si>
-    <t>CREDITO CTTOS MP INTEGRAL</t>
-  </si>
-  <si>
-    <t>50084.94</t>
-  </si>
-  <si>
-    <t>RIOS ITURRA MARIO HUMBERTO</t>
-  </si>
-  <si>
-    <t>1015733</t>
-  </si>
-  <si>
-    <t>4600000</t>
-  </si>
-  <si>
-    <t>460000</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>KATHERINE ANDREA ROMERO MILLAN</t>
-  </si>
-  <si>
-    <t>200000</t>
-  </si>
-  <si>
-    <t>FUENTES ARAYA BEATRIZ DE LAS MERCEDEZ</t>
-  </si>
-  <si>
-    <t>1015724</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>CARRASCO HERNANDEZ MARTA</t>
-  </si>
-  <si>
-    <t>1015719</t>
-  </si>
-  <si>
-    <t>ANDREA VALESKA SAFFA ROMERO</t>
-  </si>
-  <si>
-    <t>LOPEZ RUZ ENRIQUE ANTONIO</t>
-  </si>
-  <si>
-    <t>1015721</t>
-  </si>
-  <si>
-    <t>3992000</t>
-  </si>
-  <si>
-    <t>400000</t>
-  </si>
-  <si>
-    <t>3592000</t>
-  </si>
-  <si>
-    <t>Betzabeth nicole chacon quinteros</t>
-  </si>
-  <si>
-    <t>PROMOCION CREDITO CTTOS</t>
-  </si>
-  <si>
-    <t>GAETE OSORIO MARINA DE LAS MERCEDES</t>
-  </si>
-  <si>
-    <t>1015720</t>
-  </si>
-  <si>
-    <t>Margarita Cristina Rojas Quezada</t>
-  </si>
-  <si>
-    <t>810000</t>
-  </si>
-  <si>
-    <t>PEÑALOZA SANDOVAL ELBA ANGELA</t>
-  </si>
-  <si>
-    <t>1015732</t>
-  </si>
-  <si>
-    <t>3220000</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>CONTADO CTTOS</t>
+    <t>36674</t>
+  </si>
+  <si>
+    <t>7-A-030</t>
+  </si>
+  <si>
+    <t>Valle del Descanso</t>
+  </si>
+  <si>
+    <t>1015610</t>
+  </si>
+  <si>
+    <t>YIPSY JOSE BRITO MARIN</t>
+  </si>
+  <si>
+    <t>LOPEZ RUIZ SILVIA TERESA</t>
+  </si>
+  <si>
+    <t>10557587-4</t>
+  </si>
+  <si>
+    <t>Juan de Dios marticorena, ALT 6 - Lampa -</t>
+  </si>
+  <si>
+    <t>942671991</t>
+  </si>
+  <si>
+    <t>stlopezr1@gmail.com</t>
+  </si>
+  <si>
+    <t>310500</t>
+  </si>
+  <si>
+    <t>345000</t>
+  </si>
+  <si>
+    <t>3105000</t>
+  </si>
+  <si>
+    <t>2794500</t>
+  </si>
+  <si>
+    <t>58218.75</t>
+  </si>
+  <si>
+    <t>04/04/2026</t>
+  </si>
+  <si>
+    <t>7-A-032</t>
+  </si>
+  <si>
+    <t>1015609</t>
+  </si>
+  <si>
+    <t>GALAZ ORELLANA YSKRA</t>
+  </si>
+  <si>
+    <t>12859425-6</t>
+  </si>
+  <si>
+    <t>El boldo 8064, Lo Prado, Santiago, Metropolitana  Pi/dp Block 15 Casa:</t>
+  </si>
+  <si>
+    <t>999250322</t>
+  </si>
+  <si>
+    <t>gatubela1@live.cl</t>
+  </si>
+  <si>
+    <t>618000</t>
+  </si>
+  <si>
+    <t>17.91</t>
+  </si>
+  <si>
+    <t>2832000</t>
+  </si>
+  <si>
+    <t>2532000</t>
+  </si>
+  <si>
+    <t>35143</t>
+  </si>
+  <si>
+    <t>7-A-033</t>
+  </si>
+  <si>
+    <t>1015697</t>
+  </si>
+  <si>
+    <t>890000</t>
+  </si>
+  <si>
+    <t>17.84</t>
+  </si>
+  <si>
+    <t>4100000</t>
+  </si>
+  <si>
+    <t>3601000</t>
+  </si>
+  <si>
+    <t>75013</t>
+  </si>
+  <si>
+    <t>1-AO-16</t>
+  </si>
+  <si>
+    <t>Valles De las Rosas</t>
+  </si>
+  <si>
+    <t>1015681</t>
+  </si>
+  <si>
+    <t>IBAÑEZ NUÑEZ CONSTANZA JANICE</t>
+  </si>
+  <si>
+    <t>17680901-9</t>
+  </si>
+  <si>
+    <t>Antonio Maceo 3176, ALT 3176 - Renca -</t>
+  </si>
+  <si>
+    <t>933158189</t>
+  </si>
+  <si>
+    <t>constanzajanice@gmaim.com</t>
+  </si>
+  <si>
+    <t>600000</t>
+  </si>
+  <si>
+    <t>5280000</t>
+  </si>
+  <si>
+    <t>146655</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>1-X-18</t>
+  </si>
+  <si>
+    <t>1015686</t>
+  </si>
+  <si>
+    <t>449853.97</t>
+  </si>
+  <si>
+    <t>GALLARDO CONTRERAS SILVIA ISABEL</t>
+  </si>
+  <si>
+    <t>10740648-4</t>
+  </si>
+  <si>
+    <t>LOS ROBLES 485, ALT 485 - Quilicura -</t>
+  </si>
+  <si>
+    <t>964469773</t>
+  </si>
+  <si>
+    <t>975782194</t>
+  </si>
+  <si>
+    <t>sigallardo28@hotmail.com</t>
+  </si>
+  <si>
+    <t>0.34</t>
+  </si>
+  <si>
+    <t>3880000</t>
+  </si>
+  <si>
+    <t>107770</t>
+  </si>
+  <si>
+    <t>2-AA-4</t>
+  </si>
+  <si>
+    <t>Valles de Las Rosas 2</t>
+  </si>
+  <si>
+    <t>2026-03-25T00:00:00</t>
+  </si>
+  <si>
+    <t>1015620</t>
+  </si>
+  <si>
+    <t>BARRA GONZALEZ OSCAR. LEONEL</t>
+  </si>
+  <si>
+    <t>10089841-1</t>
+  </si>
+  <si>
+    <t>Pje talinay, ALT 716 - Quilicura -</t>
+  </si>
+  <si>
+    <t>962035674</t>
+  </si>
+  <si>
+    <t>oscarleonelbarragonzalez@gmail.com</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>2-AH-15</t>
+  </si>
+  <si>
+    <t>1015605</t>
+  </si>
+  <si>
+    <t>REYES RUZ ANTONIETA BEATRIZ</t>
+  </si>
+  <si>
+    <t>9981219-2</t>
+  </si>
+  <si>
+    <t>Manuel Antonio Matta 0620, ALT 13 - Quilicura -</t>
+  </si>
+  <si>
+    <t>972986441</t>
+  </si>
+  <si>
+    <t>resssntonieta@gmail.com - ressntonieta@hmail.com</t>
+  </si>
+  <si>
+    <t>324350</t>
+  </si>
+  <si>
+    <t>0.07</t>
+  </si>
+  <si>
+    <t>4665650</t>
+  </si>
+  <si>
+    <t>64779</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>2-AI-13</t>
+  </si>
+  <si>
+    <t>1015634</t>
+  </si>
+  <si>
+    <t>GERENCIA DISTRITO 2</t>
+  </si>
+  <si>
+    <t>RODOLFO SANTANA BASAEZ</t>
+  </si>
+  <si>
+    <t>JESUS RAMON VILLEGAS VILLAVICENCIO</t>
+  </si>
+  <si>
+    <t>NAVARRO ROJAS JESÚS</t>
+  </si>
+  <si>
+    <t>18026798-0</t>
+  </si>
+  <si>
+    <t>Anibal pinto, ALT 1351 - Independencia -</t>
+  </si>
+  <si>
+    <t>Independencia</t>
+  </si>
+  <si>
+    <t>944256626</t>
+  </si>
+  <si>
+    <t>monardeyasna70@gmail.com</t>
+  </si>
+  <si>
+    <t>Planes Parque Especial</t>
+  </si>
+  <si>
+    <t>Jardin Mausoleo Privado (cuotas)</t>
+  </si>
+  <si>
+    <t>Jardin Mausoleo Privado</t>
+  </si>
+  <si>
+    <t>19970000</t>
+  </si>
+  <si>
+    <t>4992500</t>
+  </si>
+  <si>
+    <t>14977500</t>
+  </si>
+  <si>
+    <t>12977500</t>
+  </si>
+  <si>
+    <t>270364.59</t>
+  </si>
+  <si>
+    <t>2-O-1</t>
+  </si>
+  <si>
+    <t>2026-03-12T00:00:00</t>
   </si>
 </sst>
 </file>
@@ -1123,13 +2854,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="12" width="12" customWidth="1"/>
+    <col min="1" max="39" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1166,391 +2897,6158 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>50</v>
+      </c>
+      <c r="M2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>54</v>
+      </c>
+      <c r="R2" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" t="s">
+        <v>56</v>
+      </c>
+      <c r="U2" t="s">
+        <v>56</v>
+      </c>
+      <c r="V2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" t="s">
+        <v>70</v>
+      </c>
+      <c r="L3" t="s">
+        <v>71</v>
+      </c>
+      <c r="M3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O3" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T3" t="s">
+        <v>74</v>
+      </c>
+      <c r="U3" t="s">
+        <v>74</v>
+      </c>
+      <c r="V3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" t="s">
+        <v>75</v>
+      </c>
+      <c r="X3" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
         <v>45</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" t="s">
-        <v>49</v>
-      </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
       </c>
       <c r="H4" t="s">
         <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
+        <v>85</v>
+      </c>
+      <c r="K4" t="s">
+        <v>86</v>
+      </c>
+      <c r="L4" t="s">
+        <v>87</v>
+      </c>
+      <c r="M4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O4" t="s">
+        <v>53</v>
+      </c>
+      <c r="P4" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S4" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" t="s">
+        <v>74</v>
+      </c>
+      <c r="U4" t="s">
+        <v>74</v>
+      </c>
+      <c r="V4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W4" t="s">
+        <v>75</v>
+      </c>
+      <c r="X4" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE4" t="s">
         <v>64</v>
       </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="AF4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" t="s">
+        <v>92</v>
+      </c>
+      <c r="I5" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" t="s">
+        <v>94</v>
+      </c>
+      <c r="L5" t="s">
+        <v>95</v>
+      </c>
+      <c r="M5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" t="s">
+        <v>97</v>
+      </c>
+      <c r="S5" t="s">
+        <v>44</v>
+      </c>
+      <c r="T5" t="s">
+        <v>98</v>
+      </c>
+      <c r="U5" t="s">
+        <v>98</v>
+      </c>
+      <c r="V5" t="s">
+        <v>57</v>
+      </c>
+      <c r="W5" t="s">
+        <v>99</v>
+      </c>
+      <c r="X5" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J6" t="s">
+        <v>111</v>
+      </c>
+      <c r="K6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N6" t="s">
+        <v>52</v>
+      </c>
+      <c r="O6" t="s">
+        <v>53</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R6" t="s">
+        <v>115</v>
+      </c>
+      <c r="S6" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" t="s">
+        <v>74</v>
+      </c>
+      <c r="U6" t="s">
+        <v>74</v>
+      </c>
+      <c r="V6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W6" t="s">
+        <v>75</v>
+      </c>
+      <c r="X6" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>121</v>
+      </c>
+      <c r="I7" t="s">
+        <v>122</v>
+      </c>
+      <c r="J7" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L7" t="s">
+        <v>125</v>
+      </c>
+      <c r="M7" t="s">
+        <v>126</v>
+      </c>
+      <c r="N7" t="s">
+        <v>127</v>
+      </c>
+      <c r="O7" t="s">
+        <v>128</v>
+      </c>
+      <c r="P7" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>129</v>
+      </c>
+      <c r="R7" t="s">
+        <v>130</v>
+      </c>
+      <c r="S7" t="s">
+        <v>44</v>
+      </c>
+      <c r="T7" t="s">
+        <v>74</v>
+      </c>
+      <c r="U7" t="s">
+        <v>74</v>
+      </c>
+      <c r="V7" t="s">
+        <v>57</v>
+      </c>
+      <c r="W7" t="s">
+        <v>75</v>
+      </c>
+      <c r="X7" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>119</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" t="s">
+        <v>110</v>
+      </c>
+      <c r="I8" t="s">
+        <v>47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>134</v>
+      </c>
+      <c r="K8" t="s">
+        <v>135</v>
+      </c>
+      <c r="L8" t="s">
+        <v>136</v>
+      </c>
+      <c r="M8" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" t="s">
+        <v>52</v>
+      </c>
+      <c r="O8" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>137</v>
+      </c>
+      <c r="R8" t="s">
+        <v>138</v>
+      </c>
+      <c r="S8" t="s">
+        <v>44</v>
+      </c>
+      <c r="T8" t="s">
+        <v>74</v>
+      </c>
+      <c r="U8" t="s">
+        <v>74</v>
+      </c>
+      <c r="V8" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" t="s">
+        <v>75</v>
+      </c>
+      <c r="X8" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J9" t="s">
+        <v>145</v>
+      </c>
+      <c r="K9" t="s">
+        <v>146</v>
+      </c>
+      <c r="L9" t="s">
+        <v>147</v>
+      </c>
+      <c r="M9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" t="s">
+        <v>148</v>
+      </c>
+      <c r="P9" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>149</v>
+      </c>
+      <c r="R9" t="s">
+        <v>150</v>
+      </c>
+      <c r="S9" t="s">
+        <v>44</v>
+      </c>
+      <c r="T9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" t="s">
+        <v>75</v>
+      </c>
+      <c r="X9" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" t="s">
+        <v>152</v>
+      </c>
+      <c r="K10" t="s">
+        <v>153</v>
+      </c>
+      <c r="L10" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" t="s">
+        <v>53</v>
+      </c>
+      <c r="P10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>155</v>
+      </c>
+      <c r="R10" t="s">
+        <v>156</v>
+      </c>
+      <c r="S10" t="s">
+        <v>44</v>
+      </c>
+      <c r="T10" t="s">
+        <v>74</v>
+      </c>
+      <c r="U10" t="s">
+        <v>74</v>
+      </c>
+      <c r="V10" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" t="s">
+        <v>75</v>
+      </c>
+      <c r="X10" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>157</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>160</v>
+      </c>
+      <c r="J11" t="s">
+        <v>161</v>
+      </c>
+      <c r="K11" t="s">
+        <v>162</v>
+      </c>
+      <c r="L11" t="s">
+        <v>163</v>
+      </c>
+      <c r="M11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" t="s">
+        <v>52</v>
+      </c>
+      <c r="O11" t="s">
+        <v>53</v>
+      </c>
+      <c r="P11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>164</v>
+      </c>
+      <c r="R11" t="s">
+        <v>165</v>
+      </c>
+      <c r="S11" t="s">
+        <v>44</v>
+      </c>
+      <c r="T11" t="s">
+        <v>74</v>
+      </c>
+      <c r="U11" t="s">
+        <v>74</v>
+      </c>
+      <c r="V11" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" t="s">
+        <v>75</v>
+      </c>
+      <c r="X11" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>169</v>
+      </c>
+      <c r="I12" t="s">
+        <v>160</v>
+      </c>
+      <c r="J12" t="s">
+        <v>170</v>
+      </c>
+      <c r="K12" t="s">
+        <v>171</v>
+      </c>
+      <c r="L12" t="s">
+        <v>172</v>
+      </c>
+      <c r="M12" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" t="s">
+        <v>52</v>
+      </c>
+      <c r="O12" t="s">
+        <v>53</v>
+      </c>
+      <c r="P12" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>174</v>
+      </c>
+      <c r="R12" t="s">
+        <v>175</v>
+      </c>
+      <c r="S12" t="s">
+        <v>44</v>
+      </c>
+      <c r="T12" t="s">
+        <v>74</v>
+      </c>
+      <c r="U12" t="s">
+        <v>74</v>
+      </c>
+      <c r="V12" t="s">
+        <v>57</v>
+      </c>
+      <c r="W12" t="s">
+        <v>75</v>
+      </c>
+      <c r="X12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I13" t="s">
+        <v>160</v>
+      </c>
+      <c r="J13" t="s">
+        <v>179</v>
+      </c>
+      <c r="K13" t="s">
+        <v>180</v>
+      </c>
+      <c r="L13" t="s">
+        <v>181</v>
+      </c>
+      <c r="M13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" t="s">
+        <v>52</v>
+      </c>
+      <c r="O13" t="s">
+        <v>53</v>
+      </c>
+      <c r="P13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>182</v>
+      </c>
+      <c r="R13" t="s">
+        <v>183</v>
+      </c>
+      <c r="S13" t="s">
+        <v>44</v>
+      </c>
+      <c r="T13" t="s">
+        <v>56</v>
+      </c>
+      <c r="U13" t="s">
+        <v>56</v>
+      </c>
+      <c r="V13" t="s">
+        <v>57</v>
+      </c>
+      <c r="W13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X13" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>187</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>188</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>190</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>191</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" t="s">
+        <v>193</v>
+      </c>
+      <c r="I14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J14" t="s">
+        <v>194</v>
+      </c>
+      <c r="K14" t="s">
+        <v>195</v>
+      </c>
+      <c r="L14" t="s">
+        <v>196</v>
+      </c>
+      <c r="M14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" t="s">
+        <v>52</v>
+      </c>
+      <c r="O14" t="s">
+        <v>197</v>
+      </c>
+      <c r="P14" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>199</v>
+      </c>
+      <c r="R14" t="s">
+        <v>200</v>
+      </c>
+      <c r="S14" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" t="s">
+        <v>74</v>
+      </c>
+      <c r="U14" t="s">
+        <v>74</v>
+      </c>
+      <c r="V14" t="s">
+        <v>57</v>
+      </c>
+      <c r="W14" t="s">
+        <v>75</v>
+      </c>
+      <c r="X14" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" t="s">
         <v>46</v>
       </c>
+      <c r="I15" t="s">
+        <v>47</v>
+      </c>
+      <c r="J15" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" t="s">
+        <v>205</v>
+      </c>
+      <c r="L15" t="s">
+        <v>206</v>
+      </c>
+      <c r="M15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" t="s">
+        <v>52</v>
+      </c>
+      <c r="O15" t="s">
+        <v>197</v>
+      </c>
+      <c r="P15" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>208</v>
+      </c>
+      <c r="R15" t="s">
+        <v>209</v>
+      </c>
+      <c r="S15" t="s">
+        <v>44</v>
+      </c>
+      <c r="T15" t="s">
+        <v>74</v>
+      </c>
+      <c r="U15" t="s">
+        <v>74</v>
+      </c>
+      <c r="V15" t="s">
+        <v>57</v>
+      </c>
+      <c r="W15" t="s">
+        <v>75</v>
+      </c>
+      <c r="X15" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>142</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>211</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>212</v>
+      </c>
+      <c r="K16" t="s">
+        <v>213</v>
+      </c>
+      <c r="L16" t="s">
+        <v>214</v>
+      </c>
+      <c r="M16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" t="s">
+        <v>215</v>
+      </c>
+      <c r="O16" t="s">
+        <v>216</v>
+      </c>
+      <c r="P16" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>218</v>
+      </c>
+      <c r="R16" t="s">
+        <v>219</v>
+      </c>
+      <c r="S16" t="s">
+        <v>44</v>
+      </c>
+      <c r="T16" t="s">
+        <v>74</v>
+      </c>
+      <c r="U16" t="s">
+        <v>74</v>
+      </c>
+      <c r="V16" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" t="s">
+        <v>75</v>
+      </c>
+      <c r="X16" t="s">
         <v>76</v>
       </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="Y16" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="s">
+      <c r="Z16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC16" t="s">
         <v>78</v>
       </c>
-      <c r="E5" t="s">
+      <c r="AD16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" t="s">
+        <v>211</v>
+      </c>
+      <c r="I17" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" t="s">
+        <v>221</v>
+      </c>
+      <c r="K17" t="s">
+        <v>222</v>
+      </c>
+      <c r="L17" t="s">
+        <v>223</v>
+      </c>
+      <c r="M17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" t="s">
+        <v>215</v>
+      </c>
+      <c r="O17" t="s">
+        <v>224</v>
+      </c>
+      <c r="P17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>225</v>
+      </c>
+      <c r="R17" t="s">
+        <v>226</v>
+      </c>
+      <c r="S17" t="s">
+        <v>44</v>
+      </c>
+      <c r="T17" t="s">
+        <v>56</v>
+      </c>
+      <c r="U17" t="s">
+        <v>56</v>
+      </c>
+      <c r="V17" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" t="s">
+        <v>58</v>
+      </c>
+      <c r="X17" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>233</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
+        <v>234</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J18" t="s">
+        <v>236</v>
+      </c>
+      <c r="K18" t="s">
+        <v>237</v>
+      </c>
+      <c r="L18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" t="s">
+        <v>126</v>
+      </c>
+      <c r="N18" t="s">
+        <v>238</v>
+      </c>
+      <c r="O18" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>239</v>
+      </c>
+      <c r="R18" t="s">
+        <v>240</v>
+      </c>
+      <c r="S18" t="s">
+        <v>44</v>
+      </c>
+      <c r="T18" t="s">
+        <v>56</v>
+      </c>
+      <c r="U18" t="s">
+        <v>56</v>
+      </c>
+      <c r="V18" t="s">
+        <v>57</v>
+      </c>
+      <c r="W18" t="s">
+        <v>58</v>
+      </c>
+      <c r="X18" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>241</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI18" t="s">
+        <v>243</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" t="s">
+        <v>235</v>
+      </c>
+      <c r="J19" t="s">
+        <v>245</v>
+      </c>
+      <c r="K19" t="s">
+        <v>246</v>
+      </c>
+      <c r="L19" t="s">
+        <v>247</v>
+      </c>
+      <c r="M19" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" t="s">
+        <v>215</v>
+      </c>
+      <c r="O19" t="s">
+        <v>224</v>
+      </c>
+      <c r="P19" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>248</v>
+      </c>
+      <c r="R19" t="s">
+        <v>249</v>
+      </c>
+      <c r="S19" t="s">
+        <v>44</v>
+      </c>
+      <c r="T19" t="s">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s">
+        <v>57</v>
+      </c>
+      <c r="W19" t="s">
+        <v>75</v>
+      </c>
+      <c r="X19" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC19" t="s">
         <v>78</v>
       </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="AD19" t="s">
         <v>79</v>
       </c>
-      <c r="H5" t="s">
+      <c r="AE19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>251</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>243</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>252</v>
+      </c>
+      <c r="C20" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20" t="s">
+        <v>254</v>
+      </c>
+      <c r="J20" t="s">
+        <v>255</v>
+      </c>
+      <c r="K20" t="s">
+        <v>256</v>
+      </c>
+      <c r="L20" t="s">
+        <v>257</v>
+      </c>
+      <c r="M20" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" t="s">
+        <v>52</v>
+      </c>
+      <c r="O20" t="s">
+        <v>258</v>
+      </c>
+      <c r="P20" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>259</v>
+      </c>
+      <c r="R20" t="s">
+        <v>260</v>
+      </c>
+      <c r="S20" t="s">
+        <v>44</v>
+      </c>
+      <c r="T20" t="s">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s">
+        <v>57</v>
+      </c>
+      <c r="W20" t="s">
+        <v>75</v>
+      </c>
+      <c r="X20" t="s">
+        <v>261</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC20" t="s">
         <v>78</v>
       </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="AD20" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG20" t="s">
+        <v>263</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>264</v>
+      </c>
+      <c r="AI20" t="s">
+        <v>265</v>
+      </c>
+      <c r="AJ20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>266</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21" t="s">
+        <v>235</v>
+      </c>
+      <c r="J21" t="s">
+        <v>268</v>
+      </c>
+      <c r="K21" t="s">
+        <v>269</v>
+      </c>
+      <c r="L21" t="s">
+        <v>270</v>
+      </c>
+      <c r="M21" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" t="s">
+        <v>52</v>
+      </c>
+      <c r="O21" t="s">
+        <v>53</v>
+      </c>
+      <c r="P21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>271</v>
+      </c>
+      <c r="R21" t="s">
+        <v>272</v>
+      </c>
+      <c r="S21" t="s">
+        <v>44</v>
+      </c>
+      <c r="T21" t="s">
+        <v>56</v>
+      </c>
+      <c r="U21" t="s">
+        <v>56</v>
+      </c>
+      <c r="V21" t="s">
+        <v>57</v>
+      </c>
+      <c r="W21" t="s">
+        <v>58</v>
+      </c>
+      <c r="X21" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>273</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG21" t="s">
+        <v>274</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>275</v>
+      </c>
+      <c r="AI21" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" t="s">
+        <v>253</v>
+      </c>
+      <c r="I22" t="s">
+        <v>144</v>
+      </c>
+      <c r="J22" t="s">
+        <v>278</v>
+      </c>
+      <c r="K22" t="s">
+        <v>279</v>
+      </c>
+      <c r="L22" t="s">
+        <v>280</v>
+      </c>
+      <c r="M22" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" t="s">
+        <v>52</v>
+      </c>
+      <c r="O22" t="s">
+        <v>53</v>
+      </c>
+      <c r="P22" t="s">
+        <v>281</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>282</v>
+      </c>
+      <c r="R22" t="s">
+        <v>283</v>
+      </c>
+      <c r="S22" t="s">
+        <v>44</v>
+      </c>
+      <c r="T22" t="s">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s">
+        <v>57</v>
+      </c>
+      <c r="W22" t="s">
+        <v>75</v>
+      </c>
+      <c r="X22" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG22" t="s">
+        <v>140</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>284</v>
+      </c>
+      <c r="AI22" t="s">
+        <v>285</v>
+      </c>
+      <c r="AJ22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>286</v>
+      </c>
+      <c r="C23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>44</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>287</v>
+      </c>
+      <c r="I23" t="s">
+        <v>288</v>
+      </c>
+      <c r="J23" t="s">
+        <v>289</v>
+      </c>
+      <c r="K23" t="s">
+        <v>290</v>
+      </c>
+      <c r="L23" t="s">
+        <v>291</v>
+      </c>
+      <c r="M23" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" t="s">
+        <v>52</v>
+      </c>
+      <c r="O23" t="s">
+        <v>53</v>
+      </c>
+      <c r="P23" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>293</v>
+      </c>
+      <c r="R23" t="s">
+        <v>294</v>
+      </c>
+      <c r="S23" t="s">
+        <v>44</v>
+      </c>
+      <c r="T23" t="s">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s">
+        <v>57</v>
+      </c>
+      <c r="W23" t="s">
+        <v>75</v>
+      </c>
+      <c r="X23" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF23" t="s">
         <v>80</v>
       </c>
-      <c r="L5" t="s">
+      <c r="AG23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI23" t="s">
+        <v>296</v>
+      </c>
+      <c r="AJ23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>297</v>
+      </c>
+      <c r="C24" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>298</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" t="s">
+        <v>299</v>
+      </c>
+      <c r="I24" t="s">
+        <v>68</v>
+      </c>
+      <c r="J24" t="s">
+        <v>300</v>
+      </c>
+      <c r="K24" t="s">
+        <v>301</v>
+      </c>
+      <c r="L24" t="s">
+        <v>302</v>
+      </c>
+      <c r="M24" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" t="s">
+        <v>52</v>
+      </c>
+      <c r="O24" t="s">
+        <v>53</v>
+      </c>
+      <c r="P24" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>303</v>
+      </c>
+      <c r="R24" t="s">
+        <v>304</v>
+      </c>
+      <c r="S24" t="s">
+        <v>44</v>
+      </c>
+      <c r="T24" t="s">
+        <v>98</v>
+      </c>
+      <c r="U24" t="s">
+        <v>98</v>
+      </c>
+      <c r="V24" t="s">
+        <v>57</v>
+      </c>
+      <c r="W24" t="s">
+        <v>99</v>
+      </c>
+      <c r="X24" t="s">
+        <v>305</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>308</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>309</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>310</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG24" t="s">
+        <v>311</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>312</v>
+      </c>
+      <c r="AI24" t="s">
+        <v>313</v>
+      </c>
+      <c r="AJ24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" t="s">
+        <v>315</v>
+      </c>
+      <c r="C25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" t="s">
+        <v>44</v>
+      </c>
+      <c r="G25" t="s">
+        <v>316</v>
+      </c>
+      <c r="H25" t="s">
+        <v>317</v>
+      </c>
+      <c r="I25" t="s">
+        <v>47</v>
+      </c>
+      <c r="J25" t="s">
+        <v>318</v>
+      </c>
+      <c r="K25" t="s">
+        <v>319</v>
+      </c>
+      <c r="L25" t="s">
+        <v>320</v>
+      </c>
+      <c r="M25" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" t="s">
+        <v>52</v>
+      </c>
+      <c r="O25" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>321</v>
+      </c>
+      <c r="R25" t="s">
+        <v>322</v>
+      </c>
+      <c r="S25" t="s">
+        <v>44</v>
+      </c>
+      <c r="T25" t="s">
+        <v>74</v>
+      </c>
+      <c r="U25" t="s">
+        <v>74</v>
+      </c>
+      <c r="V25" t="s">
+        <v>57</v>
+      </c>
+      <c r="W25" t="s">
+        <v>75</v>
+      </c>
+      <c r="X25" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC25" t="s">
         <v>78</v>
       </c>
+      <c r="AD25" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG25" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH25" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI25" t="s">
+        <v>323</v>
+      </c>
+      <c r="AJ25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM25" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" t="s">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>39</v>
       </c>
-      <c r="J6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="B26" t="s">
+        <v>324</v>
+      </c>
+      <c r="C26" t="s">
         <v>41</v>
       </c>
-      <c r="L6" t="s">
-        <v>22</v>
+      <c r="D26" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>316</v>
+      </c>
+      <c r="H26" t="s">
+        <v>317</v>
+      </c>
+      <c r="I26" t="s">
+        <v>47</v>
+      </c>
+      <c r="J26" t="s">
+        <v>325</v>
+      </c>
+      <c r="K26" t="s">
+        <v>326</v>
+      </c>
+      <c r="L26" t="s">
+        <v>327</v>
+      </c>
+      <c r="M26" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" t="s">
+        <v>52</v>
+      </c>
+      <c r="O26" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>328</v>
+      </c>
+      <c r="R26" t="s">
+        <v>329</v>
+      </c>
+      <c r="S26" t="s">
+        <v>44</v>
+      </c>
+      <c r="T26" t="s">
+        <v>74</v>
+      </c>
+      <c r="U26" t="s">
+        <v>74</v>
+      </c>
+      <c r="V26" t="s">
+        <v>57</v>
+      </c>
+      <c r="W26" t="s">
+        <v>75</v>
+      </c>
+      <c r="X26" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>78</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG26" t="s">
+        <v>131</v>
+      </c>
+      <c r="AH26" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI26" t="s">
+        <v>323</v>
+      </c>
+      <c r="AJ26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" t="s">
+        <v>330</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" t="s">
         <v>43</v>
       </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="F27" t="s">
+        <v>44</v>
+      </c>
+      <c r="G27" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" t="s">
+        <v>331</v>
+      </c>
+      <c r="I27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" t="s">
+        <v>332</v>
+      </c>
+      <c r="K27" t="s">
+        <v>333</v>
+      </c>
+      <c r="L27" t="s">
+        <v>334</v>
+      </c>
+      <c r="M27" t="s">
+        <v>335</v>
+      </c>
+      <c r="N27" t="s">
+        <v>336</v>
+      </c>
+      <c r="O27" t="s">
+        <v>336</v>
+      </c>
+      <c r="P27" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>337</v>
+      </c>
+      <c r="R27" t="s">
+        <v>338</v>
+      </c>
+      <c r="S27" t="s">
+        <v>44</v>
+      </c>
+      <c r="T27" t="s">
+        <v>56</v>
+      </c>
+      <c r="U27" t="s">
+        <v>56</v>
+      </c>
+      <c r="V27" t="s">
+        <v>57</v>
+      </c>
+      <c r="W27" t="s">
+        <v>58</v>
+      </c>
+      <c r="X27" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>339</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>230</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>284</v>
+      </c>
+      <c r="AG27" t="s">
+        <v>340</v>
+      </c>
+      <c r="AH27" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI27" t="s">
+        <v>323</v>
+      </c>
+      <c r="AJ27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM27" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" t="s">
+        <v>342</v>
+      </c>
+      <c r="D28" t="s">
+        <v>133</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
         <v>45</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H28" t="s">
+        <v>343</v>
+      </c>
+      <c r="I28" t="s">
+        <v>44</v>
+      </c>
+      <c r="J28" t="s">
+        <v>344</v>
+      </c>
+      <c r="K28" t="s">
+        <v>345</v>
+      </c>
+      <c r="L28" t="s">
+        <v>346</v>
+      </c>
+      <c r="M28" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" t="s">
+        <v>215</v>
+      </c>
+      <c r="O28" t="s">
+        <v>224</v>
+      </c>
+      <c r="P28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>347</v>
+      </c>
+      <c r="R28" t="s">
+        <v>348</v>
+      </c>
+      <c r="S28" t="s">
+        <v>44</v>
+      </c>
+      <c r="T28" t="s">
+        <v>56</v>
+      </c>
+      <c r="U28" t="s">
+        <v>56</v>
+      </c>
+      <c r="V28" t="s">
+        <v>57</v>
+      </c>
+      <c r="W28" t="s">
+        <v>58</v>
+      </c>
+      <c r="X28" t="s">
+        <v>227</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>284</v>
+      </c>
+      <c r="AG28" t="s">
+        <v>349</v>
+      </c>
+      <c r="AH28" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI28" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AK28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AL28" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM28" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" t="s">
+        <v>352</v>
+      </c>
+      <c r="C29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" t="s">
+        <v>45</v>
+      </c>
+      <c r="H29" t="s">
         <v>46</v>
       </c>
-      <c r="F7" t="s">
+      <c r="I29" t="s">
+        <v>68</v>
+      </c>
+      <c r="J29" t="s">
+        <v>85</v>
+      </c>
+      <c r="K29" t="s">
+        <v>86</v>
+      </c>
+      <c r="L29" t="s">
+        <v>87</v>
+      </c>
+      <c r="M29" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" t="s">
+        <v>52</v>
+      </c>
+      <c r="O29" t="s">
+        <v>53</v>
+      </c>
+      <c r="P29" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>88</v>
+      </c>
+      <c r="R29" t="s">
+        <v>89</v>
+      </c>
+      <c r="S29" t="s">
+        <v>353</v>
+      </c>
+      <c r="T29" t="s">
+        <v>354</v>
+      </c>
+      <c r="U29" t="s">
+        <v>355</v>
+      </c>
+      <c r="V29" t="s">
+        <v>57</v>
+      </c>
+      <c r="W29" t="s">
+        <v>356</v>
+      </c>
+      <c r="X29" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>358</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>356</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>356</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>359</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG29" t="s">
+        <v>360</v>
+      </c>
+      <c r="AH29" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI29" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ29" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK29" t="s">
+        <v>362</v>
+      </c>
+      <c r="AL29" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>364</v>
+      </c>
+      <c r="C30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" t="s">
+        <v>365</v>
+      </c>
+      <c r="I30" t="s">
+        <v>68</v>
+      </c>
+      <c r="J30" t="s">
+        <v>366</v>
+      </c>
+      <c r="K30" t="s">
+        <v>367</v>
+      </c>
+      <c r="L30" t="s">
+        <v>368</v>
+      </c>
+      <c r="M30" t="s">
+        <v>51</v>
+      </c>
+      <c r="N30" t="s">
+        <v>52</v>
+      </c>
+      <c r="O30" t="s">
+        <v>53</v>
+      </c>
+      <c r="P30" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>369</v>
+      </c>
+      <c r="R30" t="s">
+        <v>370</v>
+      </c>
+      <c r="S30" t="s">
+        <v>353</v>
+      </c>
+      <c r="T30" t="s">
+        <v>371</v>
+      </c>
+      <c r="U30" t="s">
+        <v>372</v>
+      </c>
+      <c r="V30" t="s">
+        <v>57</v>
+      </c>
+      <c r="W30" t="s">
+        <v>373</v>
+      </c>
+      <c r="X30" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>377</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG30" t="s">
+        <v>378</v>
+      </c>
+      <c r="AH30" t="s">
+        <v>82</v>
+      </c>
+      <c r="AI30" t="s">
+        <v>83</v>
+      </c>
+      <c r="AJ30" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK30" t="s">
+        <v>362</v>
+      </c>
+      <c r="AL30" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s">
+        <v>44</v>
+      </c>
+      <c r="G31" t="s">
+        <v>316</v>
+      </c>
+      <c r="H31" t="s">
+        <v>380</v>
+      </c>
+      <c r="I31" t="s">
+        <v>288</v>
+      </c>
+      <c r="J31" t="s">
+        <v>381</v>
+      </c>
+      <c r="K31" t="s">
+        <v>382</v>
+      </c>
+      <c r="L31" t="s">
+        <v>383</v>
+      </c>
+      <c r="M31" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" t="s">
+        <v>52</v>
+      </c>
+      <c r="O31" t="s">
+        <v>384</v>
+      </c>
+      <c r="P31" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>385</v>
+      </c>
+      <c r="R31" t="s">
+        <v>386</v>
+      </c>
+      <c r="S31" t="s">
+        <v>353</v>
+      </c>
+      <c r="T31" t="s">
+        <v>387</v>
+      </c>
+      <c r="U31" t="s">
+        <v>388</v>
+      </c>
+      <c r="V31" t="s">
+        <v>57</v>
+      </c>
+      <c r="W31" t="s">
+        <v>389</v>
+      </c>
+      <c r="X31" t="s">
+        <v>390</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>389</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>389</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>391</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG31" t="s">
+        <v>392</v>
+      </c>
+      <c r="AH31" t="s">
+        <v>393</v>
+      </c>
+      <c r="AI31" t="s">
+        <v>394</v>
+      </c>
+      <c r="AJ31" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK31" t="s">
+        <v>362</v>
+      </c>
+      <c r="AL31" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s">
+        <v>395</v>
+      </c>
+      <c r="C32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
+      </c>
+      <c r="H32" t="s">
+        <v>396</v>
+      </c>
+      <c r="I32" t="s">
+        <v>288</v>
+      </c>
+      <c r="J32" t="s">
+        <v>397</v>
+      </c>
+      <c r="K32" t="s">
+        <v>398</v>
+      </c>
+      <c r="L32" t="s">
+        <v>399</v>
+      </c>
+      <c r="M32" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" t="s">
+        <v>52</v>
+      </c>
+      <c r="O32" t="s">
+        <v>400</v>
+      </c>
+      <c r="P32" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>402</v>
+      </c>
+      <c r="R32" t="s">
+        <v>403</v>
+      </c>
+      <c r="S32" t="s">
+        <v>353</v>
+      </c>
+      <c r="T32" t="s">
+        <v>387</v>
+      </c>
+      <c r="U32" t="s">
+        <v>388</v>
+      </c>
+      <c r="V32" t="s">
+        <v>57</v>
+      </c>
+      <c r="W32" t="s">
+        <v>389</v>
+      </c>
+      <c r="X32" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>404</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>405</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>406</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>406</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>406</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>407</v>
+      </c>
+      <c r="AG32" t="s">
+        <v>406</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI32" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ32" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK32" t="s">
+        <v>362</v>
+      </c>
+      <c r="AL32" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>409</v>
+      </c>
+      <c r="C33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" t="s">
+        <v>43</v>
+      </c>
+      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" t="s">
+        <v>121</v>
+      </c>
+      <c r="I33" t="s">
+        <v>160</v>
+      </c>
+      <c r="J33" t="s">
+        <v>410</v>
+      </c>
+      <c r="K33" t="s">
+        <v>411</v>
+      </c>
+      <c r="L33" t="s">
+        <v>412</v>
+      </c>
+      <c r="M33" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" t="s">
+        <v>215</v>
+      </c>
+      <c r="O33" t="s">
+        <v>224</v>
+      </c>
+      <c r="P33" t="s">
+        <v>413</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>413</v>
+      </c>
+      <c r="R33" t="s">
+        <v>414</v>
+      </c>
+      <c r="S33" t="s">
+        <v>353</v>
+      </c>
+      <c r="T33" t="s">
+        <v>371</v>
+      </c>
+      <c r="U33" t="s">
+        <v>372</v>
+      </c>
+      <c r="V33" t="s">
+        <v>57</v>
+      </c>
+      <c r="W33" t="s">
+        <v>373</v>
+      </c>
+      <c r="X33" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>377</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG33" t="s">
+        <v>415</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI33" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ33" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK33" t="s">
+        <v>362</v>
+      </c>
+      <c r="AL33" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM33" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" t="s">
+        <v>342</v>
+      </c>
+      <c r="D34" t="s">
+        <v>417</v>
+      </c>
+      <c r="E34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+      <c r="G34" t="s">
+        <v>66</v>
+      </c>
+      <c r="H34" t="s">
+        <v>67</v>
+      </c>
+      <c r="I34" t="s">
+        <v>44</v>
+      </c>
+      <c r="J34" t="s">
+        <v>418</v>
+      </c>
+      <c r="K34" t="s">
+        <v>419</v>
+      </c>
+      <c r="L34" t="s">
+        <v>420</v>
+      </c>
+      <c r="M34" t="s">
+        <v>51</v>
+      </c>
+      <c r="N34" t="s">
+        <v>52</v>
+      </c>
+      <c r="O34" t="s">
+        <v>53</v>
+      </c>
+      <c r="P34" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>421</v>
+      </c>
+      <c r="R34" t="s">
+        <v>422</v>
+      </c>
+      <c r="S34" t="s">
+        <v>353</v>
+      </c>
+      <c r="T34" t="s">
+        <v>371</v>
+      </c>
+      <c r="U34" t="s">
+        <v>372</v>
+      </c>
+      <c r="V34" t="s">
+        <v>57</v>
+      </c>
+      <c r="W34" t="s">
+        <v>373</v>
+      </c>
+      <c r="X34" t="s">
+        <v>423</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>424</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>426</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG34" t="s">
+        <v>427</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>428</v>
+      </c>
+      <c r="AI34" t="s">
+        <v>429</v>
+      </c>
+      <c r="AJ34" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK34" t="s">
+        <v>362</v>
+      </c>
+      <c r="AL34" t="s">
+        <v>363</v>
+      </c>
+      <c r="AM34" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>431</v>
+      </c>
+      <c r="C35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" t="s">
+        <v>432</v>
+      </c>
+      <c r="F35" t="s">
+        <v>432</v>
+      </c>
+      <c r="G35" t="s">
+        <v>433</v>
+      </c>
+      <c r="H35" t="s">
+        <v>434</v>
+      </c>
+      <c r="I35" t="s">
         <v>47</v>
       </c>
-      <c r="G7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J35" t="s">
+        <v>435</v>
+      </c>
+      <c r="K35" t="s">
+        <v>436</v>
+      </c>
+      <c r="L35" t="s">
+        <v>437</v>
+      </c>
+      <c r="M35" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" t="s">
+        <v>52</v>
+      </c>
+      <c r="O35" t="s">
+        <v>53</v>
+      </c>
+      <c r="P35" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>438</v>
+      </c>
+      <c r="R35" t="s">
+        <v>439</v>
+      </c>
+      <c r="S35" t="s">
+        <v>353</v>
+      </c>
+      <c r="T35" t="s">
+        <v>371</v>
+      </c>
+      <c r="U35" t="s">
+        <v>372</v>
+      </c>
+      <c r="V35" t="s">
+        <v>57</v>
+      </c>
+      <c r="W35" t="s">
+        <v>373</v>
+      </c>
+      <c r="X35" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>424</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>376</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>440</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ35" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK35" t="s">
+        <v>442</v>
+      </c>
+      <c r="AL35" t="s">
+        <v>443</v>
+      </c>
+      <c r="AM35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>39</v>
       </c>
-      <c r="J7" t="s">
-        <v>40</v>
-      </c>
-      <c r="K7" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" t="s">
-        <v>58</v>
+      <c r="B36" t="s">
+        <v>444</v>
+      </c>
+      <c r="C36" t="s">
+        <v>342</v>
+      </c>
+      <c r="D36" t="s">
+        <v>445</v>
+      </c>
+      <c r="E36" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" t="s">
+        <v>44</v>
+      </c>
+      <c r="G36" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" t="s">
+        <v>365</v>
+      </c>
+      <c r="I36" t="s">
+        <v>44</v>
+      </c>
+      <c r="J36" t="s">
+        <v>446</v>
+      </c>
+      <c r="K36" t="s">
+        <v>447</v>
+      </c>
+      <c r="L36" t="s">
+        <v>448</v>
+      </c>
+      <c r="M36" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" t="s">
+        <v>52</v>
+      </c>
+      <c r="O36" t="s">
+        <v>53</v>
+      </c>
+      <c r="P36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>449</v>
+      </c>
+      <c r="R36" t="s">
+        <v>450</v>
+      </c>
+      <c r="S36" t="s">
+        <v>353</v>
+      </c>
+      <c r="T36" t="s">
+        <v>371</v>
+      </c>
+      <c r="U36" t="s">
+        <v>372</v>
+      </c>
+      <c r="V36" t="s">
+        <v>57</v>
+      </c>
+      <c r="W36" t="s">
+        <v>373</v>
+      </c>
+      <c r="X36" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>377</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>451</v>
+      </c>
+      <c r="AG36" t="s">
+        <v>452</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>361</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>453</v>
+      </c>
+      <c r="AJ36" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK36" t="s">
+        <v>454</v>
+      </c>
+      <c r="AL36" t="s">
+        <v>443</v>
+      </c>
+      <c r="AM36" t="s">
+        <v>455</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>456</v>
+      </c>
+      <c r="C37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" t="s">
+        <v>44</v>
+      </c>
+      <c r="H37" t="s">
+        <v>396</v>
+      </c>
+      <c r="I37" t="s">
+        <v>288</v>
+      </c>
+      <c r="J37" t="s">
+        <v>457</v>
+      </c>
+      <c r="K37" t="s">
+        <v>458</v>
+      </c>
+      <c r="L37" t="s">
+        <v>459</v>
+      </c>
+      <c r="M37" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" t="s">
+        <v>52</v>
+      </c>
+      <c r="O37" t="s">
+        <v>148</v>
+      </c>
+      <c r="P37" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>460</v>
+      </c>
+      <c r="R37" t="s">
+        <v>461</v>
+      </c>
+      <c r="S37" t="s">
+        <v>353</v>
+      </c>
+      <c r="T37" t="s">
+        <v>371</v>
+      </c>
+      <c r="U37" t="s">
+        <v>372</v>
+      </c>
+      <c r="V37" t="s">
+        <v>57</v>
+      </c>
+      <c r="W37" t="s">
+        <v>373</v>
+      </c>
+      <c r="X37" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>462</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>463</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>261</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>261</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>407</v>
+      </c>
+      <c r="AG37" t="s">
+        <v>261</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ37" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK37" t="s">
+        <v>464</v>
+      </c>
+      <c r="AL37" t="s">
+        <v>443</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>465</v>
+      </c>
+      <c r="C38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" t="s">
+        <v>466</v>
+      </c>
+      <c r="E38" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" t="s">
+        <v>396</v>
+      </c>
+      <c r="I38" t="s">
+        <v>47</v>
+      </c>
+      <c r="J38" t="s">
+        <v>467</v>
+      </c>
+      <c r="K38" t="s">
+        <v>468</v>
+      </c>
+      <c r="L38" t="s">
+        <v>469</v>
+      </c>
+      <c r="M38" t="s">
+        <v>126</v>
+      </c>
+      <c r="N38" t="s">
+        <v>127</v>
+      </c>
+      <c r="O38" t="s">
+        <v>470</v>
+      </c>
+      <c r="P38" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>472</v>
+      </c>
+      <c r="R38" t="s">
+        <v>473</v>
+      </c>
+      <c r="S38" t="s">
+        <v>353</v>
+      </c>
+      <c r="T38" t="s">
+        <v>371</v>
+      </c>
+      <c r="U38" t="s">
+        <v>372</v>
+      </c>
+      <c r="V38" t="s">
+        <v>57</v>
+      </c>
+      <c r="W38" t="s">
+        <v>373</v>
+      </c>
+      <c r="X38" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>474</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>475</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>466</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>466</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>466</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>407</v>
+      </c>
+      <c r="AG38" t="s">
+        <v>466</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>47</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK38" t="s">
+        <v>476</v>
+      </c>
+      <c r="AL38" t="s">
+        <v>443</v>
+      </c>
+      <c r="AM38" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>478</v>
+      </c>
+      <c r="C39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G39" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39" t="s">
+        <v>479</v>
+      </c>
+      <c r="I39" t="s">
+        <v>47</v>
+      </c>
+      <c r="J39" t="s">
+        <v>480</v>
+      </c>
+      <c r="K39" t="s">
+        <v>481</v>
+      </c>
+      <c r="L39" t="s">
+        <v>482</v>
+      </c>
+      <c r="M39" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" t="s">
+        <v>52</v>
+      </c>
+      <c r="O39" t="s">
+        <v>53</v>
+      </c>
+      <c r="P39" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>483</v>
+      </c>
+      <c r="R39" t="s">
+        <v>484</v>
+      </c>
+      <c r="S39" t="s">
+        <v>353</v>
+      </c>
+      <c r="T39" t="s">
+        <v>371</v>
+      </c>
+      <c r="U39" t="s">
+        <v>372</v>
+      </c>
+      <c r="V39" t="s">
+        <v>57</v>
+      </c>
+      <c r="W39" t="s">
+        <v>373</v>
+      </c>
+      <c r="X39" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>373</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>486</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG39" t="s">
+        <v>487</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK39" t="s">
+        <v>488</v>
+      </c>
+      <c r="AL39" t="s">
+        <v>443</v>
+      </c>
+      <c r="AM39" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>489</v>
+      </c>
+      <c r="C40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40" t="s">
+        <v>432</v>
+      </c>
+      <c r="F40" t="s">
+        <v>432</v>
+      </c>
+      <c r="G40" t="s">
+        <v>433</v>
+      </c>
+      <c r="H40" t="s">
+        <v>434</v>
+      </c>
+      <c r="I40" t="s">
+        <v>47</v>
+      </c>
+      <c r="J40" t="s">
+        <v>490</v>
+      </c>
+      <c r="K40" t="s">
+        <v>491</v>
+      </c>
+      <c r="L40" t="s">
+        <v>492</v>
+      </c>
+      <c r="M40" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" t="s">
+        <v>52</v>
+      </c>
+      <c r="O40" t="s">
+        <v>53</v>
+      </c>
+      <c r="P40" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>493</v>
+      </c>
+      <c r="R40" t="s">
+        <v>494</v>
+      </c>
+      <c r="S40" t="s">
+        <v>353</v>
+      </c>
+      <c r="T40" t="s">
+        <v>371</v>
+      </c>
+      <c r="U40" t="s">
+        <v>372</v>
+      </c>
+      <c r="V40" t="s">
+        <v>57</v>
+      </c>
+      <c r="W40" t="s">
+        <v>373</v>
+      </c>
+      <c r="X40" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>424</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>495</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG40" t="s">
+        <v>496</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>118</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>141</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>497</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>498</v>
+      </c>
+      <c r="AL40" t="s">
+        <v>499</v>
+      </c>
+      <c r="AM40" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>500</v>
+      </c>
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" t="s">
+        <v>44</v>
+      </c>
+      <c r="G41" t="s">
         <v>66</v>
       </c>
-      <c r="D8" t="s">
+      <c r="H41" t="s">
+        <v>299</v>
+      </c>
+      <c r="I41" t="s">
+        <v>47</v>
+      </c>
+      <c r="J41" t="s">
+        <v>501</v>
+      </c>
+      <c r="K41" t="s">
+        <v>502</v>
+      </c>
+      <c r="L41" t="s">
+        <v>503</v>
+      </c>
+      <c r="M41" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" t="s">
+        <v>52</v>
+      </c>
+      <c r="O41" t="s">
+        <v>53</v>
+      </c>
+      <c r="P41" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>505</v>
+      </c>
+      <c r="R41" t="s">
+        <v>506</v>
+      </c>
+      <c r="S41" t="s">
+        <v>353</v>
+      </c>
+      <c r="T41" t="s">
+        <v>371</v>
+      </c>
+      <c r="U41" t="s">
+        <v>372</v>
+      </c>
+      <c r="V41" t="s">
+        <v>57</v>
+      </c>
+      <c r="W41" t="s">
+        <v>373</v>
+      </c>
+      <c r="X41" t="s">
+        <v>357</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>374</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>375</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>376</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>376</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>377</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG41" t="s">
+        <v>507</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>508</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>509</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>497</v>
+      </c>
+      <c r="AK41" t="s">
+        <v>510</v>
+      </c>
+      <c r="AL41" t="s">
+        <v>499</v>
+      </c>
+      <c r="AM41" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="42" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
+        <v>511</v>
+      </c>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42" t="s">
+        <v>432</v>
+      </c>
+      <c r="F42" t="s">
+        <v>432</v>
+      </c>
+      <c r="G42" t="s">
+        <v>433</v>
+      </c>
+      <c r="H42" t="s">
+        <v>434</v>
+      </c>
+      <c r="I42" t="s">
+        <v>512</v>
+      </c>
+      <c r="J42" t="s">
+        <v>513</v>
+      </c>
+      <c r="K42" t="s">
+        <v>514</v>
+      </c>
+      <c r="L42" t="s">
+        <v>515</v>
+      </c>
+      <c r="M42" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" t="s">
+        <v>52</v>
+      </c>
+      <c r="O42" t="s">
+        <v>53</v>
+      </c>
+      <c r="P42" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>516</v>
+      </c>
+      <c r="R42" t="s">
+        <v>517</v>
+      </c>
+      <c r="S42" t="s">
+        <v>353</v>
+      </c>
+      <c r="T42" t="s">
+        <v>371</v>
+      </c>
+      <c r="U42" t="s">
+        <v>372</v>
+      </c>
+      <c r="V42" t="s">
+        <v>57</v>
+      </c>
+      <c r="W42" t="s">
+        <v>373</v>
+      </c>
+      <c r="X42" t="s">
+        <v>518</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>519</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>424</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>520</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>250</v>
+      </c>
+      <c r="AG42" t="s">
+        <v>521</v>
+      </c>
+      <c r="AH42" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI42" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>522</v>
+      </c>
+      <c r="AL42" t="s">
+        <v>499</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="43" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
+        <v>523</v>
+      </c>
+      <c r="C43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" t="s">
         <v>67</v>
       </c>
-      <c r="E8" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="I43" t="s">
+        <v>47</v>
+      </c>
+      <c r="J43" t="s">
+        <v>524</v>
+      </c>
+      <c r="K43" t="s">
+        <v>525</v>
+      </c>
+      <c r="L43" t="s">
+        <v>526</v>
+      </c>
+      <c r="M43" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" t="s">
+        <v>52</v>
+      </c>
+      <c r="O43" t="s">
+        <v>53</v>
+      </c>
+      <c r="P43" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>527</v>
+      </c>
+      <c r="R43" t="s">
+        <v>528</v>
+      </c>
+      <c r="S43" t="s">
+        <v>353</v>
+      </c>
+      <c r="T43" t="s">
+        <v>529</v>
+      </c>
+      <c r="U43" t="s">
+        <v>530</v>
+      </c>
+      <c r="V43" t="s">
+        <v>57</v>
+      </c>
+      <c r="W43" t="s">
+        <v>531</v>
+      </c>
+      <c r="X43" t="s">
+        <v>532</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>533</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>534</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>535</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>535</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>536</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG43" t="s">
+        <v>537</v>
+      </c>
+      <c r="AH43" t="s">
+        <v>538</v>
+      </c>
+      <c r="AI43" t="s">
+        <v>539</v>
+      </c>
+      <c r="AJ43" t="s">
+        <v>497</v>
+      </c>
+      <c r="AK43" t="s">
+        <v>540</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>541</v>
+      </c>
+      <c r="AM43" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
-      <c r="J8" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L8" t="s">
-        <v>68</v>
+      <c r="B44" t="s">
+        <v>542</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>543</v>
+      </c>
+      <c r="E44" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" t="s">
+        <v>45</v>
+      </c>
+      <c r="H44" t="s">
+        <v>544</v>
+      </c>
+      <c r="I44" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" t="s">
+        <v>545</v>
+      </c>
+      <c r="K44" t="s">
+        <v>546</v>
+      </c>
+      <c r="L44" t="s">
+        <v>547</v>
+      </c>
+      <c r="M44" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" t="s">
+        <v>52</v>
+      </c>
+      <c r="O44" t="s">
+        <v>548</v>
+      </c>
+      <c r="P44" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>549</v>
+      </c>
+      <c r="R44" t="s">
+        <v>550</v>
+      </c>
+      <c r="S44" t="s">
+        <v>353</v>
+      </c>
+      <c r="T44" t="s">
+        <v>354</v>
+      </c>
+      <c r="U44" t="s">
+        <v>355</v>
+      </c>
+      <c r="V44" t="s">
+        <v>57</v>
+      </c>
+      <c r="W44" t="s">
+        <v>356</v>
+      </c>
+      <c r="X44" t="s">
+        <v>551</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>552</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>103</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>553</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>553</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>554</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>451</v>
+      </c>
+      <c r="AG44" t="s">
+        <v>555</v>
+      </c>
+      <c r="AH44" t="s">
+        <v>103</v>
+      </c>
+      <c r="AI44" t="s">
+        <v>201</v>
+      </c>
+      <c r="AJ44" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK44" t="s">
+        <v>556</v>
+      </c>
+      <c r="AL44" t="s">
+        <v>557</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>477</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" t="s">
-        <v>22</v>
+    <row r="45" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" t="s">
+        <v>558</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" t="s">
+        <v>45</v>
+      </c>
+      <c r="H45" t="s">
+        <v>559</v>
+      </c>
+      <c r="I45" t="s">
+        <v>160</v>
+      </c>
+      <c r="J45" t="s">
+        <v>560</v>
+      </c>
+      <c r="K45" t="s">
+        <v>561</v>
+      </c>
+      <c r="L45" t="s">
+        <v>562</v>
+      </c>
+      <c r="M45" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" t="s">
+        <v>215</v>
+      </c>
+      <c r="O45" t="s">
+        <v>224</v>
+      </c>
+      <c r="P45" t="s">
+        <v>563</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>563</v>
+      </c>
+      <c r="R45" t="s">
+        <v>564</v>
+      </c>
+      <c r="S45" t="s">
+        <v>353</v>
+      </c>
+      <c r="T45" t="s">
+        <v>354</v>
+      </c>
+      <c r="U45" t="s">
+        <v>355</v>
+      </c>
+      <c r="V45" t="s">
+        <v>57</v>
+      </c>
+      <c r="W45" t="s">
+        <v>356</v>
+      </c>
+      <c r="X45" t="s">
+        <v>565</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>566</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>567</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>567</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>568</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG45" t="s">
+        <v>569</v>
+      </c>
+      <c r="AH45" t="s">
+        <v>497</v>
+      </c>
+      <c r="AI45" t="s">
+        <v>570</v>
+      </c>
+      <c r="AJ45" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK45" t="s">
+        <v>571</v>
+      </c>
+      <c r="AL45" t="s">
+        <v>557</v>
+      </c>
+      <c r="AM45" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" t="s">
+        <v>572</v>
+      </c>
+      <c r="C46" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" t="s">
+        <v>45</v>
+      </c>
+      <c r="H46" t="s">
+        <v>544</v>
+      </c>
+      <c r="I46" t="s">
+        <v>160</v>
+      </c>
+      <c r="J46" t="s">
+        <v>573</v>
+      </c>
+      <c r="K46" t="s">
+        <v>574</v>
+      </c>
+      <c r="L46" t="s">
+        <v>575</v>
+      </c>
+      <c r="M46" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" t="s">
         <v>52</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="O46" t="s">
+        <v>548</v>
+      </c>
+      <c r="P46" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>576</v>
+      </c>
+      <c r="R46" t="s">
+        <v>577</v>
+      </c>
+      <c r="S46" t="s">
+        <v>353</v>
+      </c>
+      <c r="T46" t="s">
+        <v>354</v>
+      </c>
+      <c r="U46" t="s">
+        <v>355</v>
+      </c>
+      <c r="V46" t="s">
+        <v>57</v>
+      </c>
+      <c r="W46" t="s">
+        <v>356</v>
+      </c>
+      <c r="X46" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>578</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>579</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>580</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>580</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>581</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>451</v>
+      </c>
+      <c r="AG46" t="s">
+        <v>582</v>
+      </c>
+      <c r="AH46" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI46" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ46" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK46" t="s">
+        <v>583</v>
+      </c>
+      <c r="AL46" t="s">
+        <v>557</v>
+      </c>
+      <c r="AM46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" t="s">
+        <v>584</v>
+      </c>
+      <c r="C47" t="s">
+        <v>41</v>
+      </c>
+      <c r="D47" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" t="s">
+        <v>316</v>
+      </c>
+      <c r="H47" t="s">
+        <v>317</v>
+      </c>
+      <c r="I47" t="s">
+        <v>47</v>
+      </c>
+      <c r="J47" t="s">
+        <v>325</v>
+      </c>
+      <c r="K47" t="s">
+        <v>326</v>
+      </c>
+      <c r="L47" t="s">
+        <v>327</v>
+      </c>
+      <c r="M47" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" t="s">
+        <v>52</v>
+      </c>
+      <c r="O47" t="s">
         <v>53</v>
       </c>
-      <c r="D10" t="s">
-        <v>54</v>
-      </c>
-      <c r="E10" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="P47" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>328</v>
+      </c>
+      <c r="R47" t="s">
+        <v>329</v>
+      </c>
+      <c r="S47" t="s">
+        <v>353</v>
+      </c>
+      <c r="T47" t="s">
+        <v>387</v>
+      </c>
+      <c r="U47" t="s">
+        <v>388</v>
+      </c>
+      <c r="V47" t="s">
         <v>57</v>
       </c>
-      <c r="K10" t="s">
+      <c r="W47" t="s">
+        <v>373</v>
+      </c>
+      <c r="X47" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>585</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>586</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>587</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>587</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>588</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG47" t="s">
+        <v>589</v>
+      </c>
+      <c r="AH47" t="s">
+        <v>275</v>
+      </c>
+      <c r="AI47" t="s">
+        <v>276</v>
+      </c>
+      <c r="AJ47" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK47" t="s">
+        <v>590</v>
+      </c>
+      <c r="AL47" t="s">
+        <v>591</v>
+      </c>
+      <c r="AM47" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" t="s">
+        <v>592</v>
+      </c>
+      <c r="C48" t="s">
         <v>41</v>
       </c>
-      <c r="L10" t="s">
-        <v>58</v>
+      <c r="D48" t="s">
+        <v>42</v>
+      </c>
+      <c r="E48" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" t="s">
+        <v>44</v>
+      </c>
+      <c r="G48" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" t="s">
+        <v>144</v>
+      </c>
+      <c r="J48" t="s">
+        <v>593</v>
+      </c>
+      <c r="K48" t="s">
+        <v>594</v>
+      </c>
+      <c r="L48" t="s">
+        <v>595</v>
+      </c>
+      <c r="M48" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" t="s">
+        <v>52</v>
+      </c>
+      <c r="O48" t="s">
+        <v>197</v>
+      </c>
+      <c r="P48" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>596</v>
+      </c>
+      <c r="R48" t="s">
+        <v>597</v>
+      </c>
+      <c r="S48" t="s">
+        <v>353</v>
+      </c>
+      <c r="T48" t="s">
+        <v>387</v>
+      </c>
+      <c r="U48" t="s">
+        <v>388</v>
+      </c>
+      <c r="V48" t="s">
+        <v>57</v>
+      </c>
+      <c r="W48" t="s">
+        <v>389</v>
+      </c>
+      <c r="X48" t="s">
+        <v>598</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>389</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>389</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>599</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG48" t="s">
+        <v>600</v>
+      </c>
+      <c r="AH48" t="s">
+        <v>601</v>
+      </c>
+      <c r="AI48" t="s">
+        <v>602</v>
+      </c>
+      <c r="AJ48" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK48" t="s">
+        <v>603</v>
+      </c>
+      <c r="AL48" t="s">
+        <v>591</v>
+      </c>
+      <c r="AM48" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" t="s">
+        <v>604</v>
+      </c>
+      <c r="C49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" t="s">
+        <v>605</v>
+      </c>
+      <c r="E49" t="s">
+        <v>44</v>
+      </c>
+      <c r="F49" t="s">
+        <v>44</v>
+      </c>
+      <c r="G49" t="s">
+        <v>44</v>
+      </c>
+      <c r="H49" t="s">
+        <v>396</v>
+      </c>
+      <c r="I49" t="s">
+        <v>254</v>
+      </c>
+      <c r="J49" t="s">
+        <v>606</v>
+      </c>
+      <c r="K49" t="s">
+        <v>607</v>
+      </c>
+      <c r="L49" t="s">
+        <v>608</v>
+      </c>
+      <c r="M49" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" t="s">
+        <v>52</v>
+      </c>
+      <c r="O49" t="s">
+        <v>53</v>
+      </c>
+      <c r="P49" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>610</v>
+      </c>
+      <c r="R49" t="s">
+        <v>611</v>
+      </c>
+      <c r="S49" t="s">
+        <v>353</v>
+      </c>
+      <c r="T49" t="s">
+        <v>387</v>
+      </c>
+      <c r="U49" t="s">
+        <v>388</v>
+      </c>
+      <c r="V49" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" t="s">
+        <v>389</v>
+      </c>
+      <c r="X49" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>612</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>389</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>389</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>613</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG49" t="s">
+        <v>614</v>
+      </c>
+      <c r="AH49" t="s">
+        <v>295</v>
+      </c>
+      <c r="AI49" t="s">
+        <v>296</v>
+      </c>
+      <c r="AJ49" t="s">
+        <v>508</v>
+      </c>
+      <c r="AK49" t="s">
+        <v>615</v>
+      </c>
+      <c r="AL49" t="s">
+        <v>616</v>
+      </c>
+      <c r="AM49" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="50" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" t="s">
+        <v>618</v>
+      </c>
+      <c r="C50" t="s">
+        <v>41</v>
+      </c>
+      <c r="D50" t="s">
+        <v>42</v>
+      </c>
+      <c r="E50" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>46</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" t="s">
-        <v>75</v>
+      <c r="F50" t="s">
+        <v>44</v>
+      </c>
+      <c r="G50" t="s">
+        <v>316</v>
+      </c>
+      <c r="H50" t="s">
+        <v>380</v>
+      </c>
+      <c r="I50" t="s">
+        <v>235</v>
+      </c>
+      <c r="J50" t="s">
+        <v>619</v>
+      </c>
+      <c r="K50" t="s">
+        <v>620</v>
+      </c>
+      <c r="L50" t="s">
+        <v>621</v>
+      </c>
+      <c r="M50" t="s">
+        <v>51</v>
+      </c>
+      <c r="N50" t="s">
+        <v>52</v>
+      </c>
+      <c r="O50" t="s">
+        <v>53</v>
+      </c>
+      <c r="P50" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>622</v>
+      </c>
+      <c r="R50" t="s">
+        <v>623</v>
+      </c>
+      <c r="S50" t="s">
+        <v>353</v>
+      </c>
+      <c r="T50" t="s">
+        <v>387</v>
+      </c>
+      <c r="U50" t="s">
+        <v>388</v>
+      </c>
+      <c r="V50" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" t="s">
+        <v>373</v>
+      </c>
+      <c r="X50" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>424</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>229</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>425</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>425</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>376</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG50" t="s">
+        <v>440</v>
+      </c>
+      <c r="AH50" t="s">
+        <v>601</v>
+      </c>
+      <c r="AI50" t="s">
+        <v>624</v>
+      </c>
+      <c r="AJ50" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK50" t="s">
+        <v>625</v>
+      </c>
+      <c r="AL50" t="s">
+        <v>616</v>
+      </c>
+      <c r="AM50" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" t="s">
+        <v>626</v>
+      </c>
+      <c r="C51" t="s">
+        <v>41</v>
+      </c>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" t="s">
+        <v>432</v>
+      </c>
+      <c r="F51" t="s">
+        <v>432</v>
+      </c>
+      <c r="G51" t="s">
+        <v>433</v>
+      </c>
+      <c r="H51" t="s">
+        <v>434</v>
+      </c>
+      <c r="I51" t="s">
+        <v>235</v>
+      </c>
+      <c r="J51" t="s">
+        <v>627</v>
+      </c>
+      <c r="K51" t="s">
+        <v>628</v>
+      </c>
+      <c r="L51" t="s">
+        <v>629</v>
+      </c>
+      <c r="M51" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" t="s">
+        <v>52</v>
+      </c>
+      <c r="O51" t="s">
+        <v>53</v>
+      </c>
+      <c r="P51" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>630</v>
+      </c>
+      <c r="R51" t="s">
+        <v>631</v>
+      </c>
+      <c r="S51" t="s">
+        <v>353</v>
+      </c>
+      <c r="T51" t="s">
+        <v>387</v>
+      </c>
+      <c r="U51" t="s">
+        <v>388</v>
+      </c>
+      <c r="V51" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" t="s">
+        <v>373</v>
+      </c>
+      <c r="X51" t="s">
+        <v>632</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>633</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>373</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>373</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>634</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>451</v>
+      </c>
+      <c r="AG51" t="s">
+        <v>635</v>
+      </c>
+      <c r="AH51" t="s">
+        <v>407</v>
+      </c>
+      <c r="AI51" t="s">
+        <v>636</v>
+      </c>
+      <c r="AJ51" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK51" t="s">
+        <v>637</v>
+      </c>
+      <c r="AL51" t="s">
+        <v>616</v>
+      </c>
+      <c r="AM51" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" t="s">
+        <v>638</v>
+      </c>
+      <c r="C52" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" t="s">
+        <v>262</v>
+      </c>
+      <c r="E52" t="s">
+        <v>639</v>
+      </c>
+      <c r="F52" t="s">
+        <v>640</v>
+      </c>
+      <c r="G52" t="s">
+        <v>641</v>
+      </c>
+      <c r="H52" t="s">
+        <v>641</v>
+      </c>
+      <c r="I52" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" t="s">
+        <v>642</v>
+      </c>
+      <c r="K52" t="s">
+        <v>643</v>
+      </c>
+      <c r="L52" t="s">
+        <v>644</v>
+      </c>
+      <c r="M52" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" t="s">
+        <v>52</v>
+      </c>
+      <c r="O52" t="s">
+        <v>645</v>
+      </c>
+      <c r="P52" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>646</v>
+      </c>
+      <c r="R52" t="s">
+        <v>647</v>
+      </c>
+      <c r="S52" t="s">
+        <v>648</v>
+      </c>
+      <c r="T52" t="s">
+        <v>649</v>
+      </c>
+      <c r="U52" t="s">
+        <v>650</v>
+      </c>
+      <c r="V52" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" t="s">
+        <v>651</v>
+      </c>
+      <c r="X52" t="s">
+        <v>262</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>652</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>295</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>653</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>653</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>654</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>107</v>
+      </c>
+      <c r="AG52" t="s">
+        <v>655</v>
+      </c>
+      <c r="AH52" t="s">
+        <v>242</v>
+      </c>
+      <c r="AI52" t="s">
+        <v>243</v>
+      </c>
+      <c r="AJ52" t="s">
+        <v>441</v>
+      </c>
+      <c r="AK52" t="s">
+        <v>656</v>
+      </c>
+      <c r="AL52" t="s">
+        <v>616</v>
+      </c>
+      <c r="AM52" t="s">
+        <v>657</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L11">
-    <sortCondition ref="I2:I11"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/datos/VENTAS_Y_ABONOS_VU.xlsx
+++ b/datos/VENTAS_Y_ABONOS_VU.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://funerariaimchile-my.sharepoint.com/personal/anais_gonzalez_funerariaim_cl/Documents/Dashboard_Control Diario de Ventas/Archivos diarios/abril/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E863AA2B-CC16-4145-A384-3A16DA2255F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EC2351E-B038-4787-A2C6-39629E12774D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ParamQuery Pro" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="290">
   <si>
     <t>EMPRESA</t>
   </si>
@@ -142,108 +155,351 @@
     <t>VALLES UNIDOS S.A.</t>
   </si>
   <si>
-    <t>1015744</t>
+    <t>1015779</t>
+  </si>
+  <si>
+    <t>ABONADO</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>GERENCIA NECESIDAD FUTURA TERRENO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Camilo Jesus Medel Rojas</t>
+  </si>
+  <si>
+    <t>daniela castro valdebenito</t>
+  </si>
+  <si>
+    <t>VENEGAS ASTORGA IRIS DEL CARMEN</t>
+  </si>
+  <si>
+    <t>11739202-3</t>
+  </si>
+  <si>
+    <t>Los espinos , ALT 138 - Lampa -</t>
+  </si>
+  <si>
+    <t>Metropolitana</t>
+  </si>
+  <si>
+    <t>Chacabuco</t>
+  </si>
+  <si>
+    <t>Lampa</t>
+  </si>
+  <si>
+    <t>931276144 - 56931276144</t>
+  </si>
+  <si>
+    <t>irisvenegas260@gmail.com - IRISVENEGAS260@GMAIL.CO</t>
+  </si>
+  <si>
+    <t>Mantención Perpetua Simple</t>
+  </si>
+  <si>
+    <t>PESOS</t>
+  </si>
+  <si>
+    <t>4600000</t>
+  </si>
+  <si>
+    <t>414000</t>
+  </si>
+  <si>
+    <t>0.09</t>
+  </si>
+  <si>
+    <t>460000</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>4140000</t>
+  </si>
+  <si>
+    <t>3478991.597</t>
+  </si>
+  <si>
+    <t>3726000</t>
+  </si>
+  <si>
+    <t>OFICINA</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>155250</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>2026-02-12T00:00:00</t>
+  </si>
+  <si>
+    <t>1015785</t>
   </si>
   <si>
     <t>COMPLETADO</t>
   </si>
   <si>
-    <t>50000</t>
-  </si>
-  <si>
-    <t>GERENCIA NECESIDAD FUTURA TERRENO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Camilo Jesus Medel Rojas</t>
-  </si>
-  <si>
-    <t>daniela castro valdebenito</t>
-  </si>
-  <si>
-    <t>VENEGAS ASTORGA IRIS DEL CARMEN</t>
-  </si>
-  <si>
-    <t>11739202-3</t>
-  </si>
-  <si>
-    <t>Los espinos , ALT 138 - Lampa -</t>
-  </si>
-  <si>
-    <t>Metropolitana</t>
-  </si>
-  <si>
-    <t>Chacabuco</t>
-  </si>
-  <si>
-    <t>Lampa</t>
-  </si>
-  <si>
-    <t>931276144 - 56931276144</t>
-  </si>
-  <si>
-    <t>irisvenegas260@gmail.com - IRISVENEGAS260@GMAIL.CO</t>
-  </si>
-  <si>
-    <t>Mantención Perpetua Simple</t>
-  </si>
-  <si>
-    <t>PESOS</t>
-  </si>
-  <si>
-    <t>4600000</t>
-  </si>
-  <si>
-    <t>414000</t>
-  </si>
-  <si>
-    <t>0.09</t>
-  </si>
-  <si>
-    <t>460000</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>4140000</t>
-  </si>
-  <si>
-    <t>3478991.597</t>
-  </si>
-  <si>
-    <t>3726000</t>
-  </si>
-  <si>
-    <t>OFICINA</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>155250</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>2026-02-12T00:00:00</t>
+    <t>Luis Alberto Osores Osores</t>
+  </si>
+  <si>
+    <t>CHAVEZ QUILODRAN SERGIO ENRIQUE</t>
+  </si>
+  <si>
+    <t>9278099-6</t>
+  </si>
+  <si>
+    <t>Pasaje vivaldi , ALT 156 - Quilicura -</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>Quilicura</t>
+  </si>
+  <si>
+    <t>942897680</t>
+  </si>
+  <si>
+    <t>kekochavezquilodran@gmail.com</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>93150</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>09/05/2026</t>
+  </si>
+  <si>
+    <t>2026-04-10T00:00:00</t>
+  </si>
+  <si>
+    <t>1015783</t>
+  </si>
+  <si>
+    <t>300000</t>
+  </si>
+  <si>
+    <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
+  </si>
+  <si>
+    <t>Yohany Margarita Gonzalez Rojas</t>
+  </si>
+  <si>
+    <t>JORQUERA VALENZUELA EMMA ROSA</t>
+  </si>
+  <si>
+    <t>67384547</t>
+  </si>
+  <si>
+    <t>Carlos dittborn, ALT 95 - Quilicura -</t>
+  </si>
+  <si>
+    <t>973382698 - +56973382698</t>
+  </si>
+  <si>
+    <t>emmajorquera2@gmail.com</t>
+  </si>
+  <si>
+    <t>Mantención Perpetua Integral</t>
+  </si>
+  <si>
+    <t>3000000</t>
+  </si>
+  <si>
+    <t>0.1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2700000</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>37500</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>2026-04-13T00:00:00</t>
+  </si>
+  <si>
+    <t>1015764</t>
+  </si>
+  <si>
+    <t>Marcela Antonia  Valdés  Barrios</t>
+  </si>
+  <si>
+    <t>14/04/2026</t>
+  </si>
+  <si>
+    <t>ALVARADO ORTIZ JACQUELINE DEL CARMEN</t>
+  </si>
+  <si>
+    <t>9765730-0</t>
+  </si>
+  <si>
+    <t>ALFREDO SANTANDER 1539, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>988574499</t>
+  </si>
+  <si>
+    <t>jacquelinealvarado356@gmail.com</t>
+  </si>
+  <si>
+    <t>2521008.4</t>
+  </si>
+  <si>
+    <t>112500</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>1015766</t>
+  </si>
+  <si>
+    <t>Rodrigo Ignacio Castro Figueroa</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ BARRIOS MARTA ORIANA</t>
+  </si>
+  <si>
+    <t>7078549-8</t>
+  </si>
+  <si>
+    <t>Psj ventana, ALT 521 - Quilicura -</t>
+  </si>
+  <si>
+    <t>987185292</t>
+  </si>
+  <si>
+    <t>223515177</t>
+  </si>
+  <si>
+    <t>martadominguezbarrios@gmail.com</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>1015780</t>
+  </si>
+  <si>
+    <t>300079.52</t>
+  </si>
+  <si>
+    <t>NF CARTERA</t>
+  </si>
+  <si>
+    <t>FLORES AEDO VALERIA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>12512126-8</t>
+  </si>
+  <si>
+    <t>PJE OLLAGUE BLOK 251 DPT A-31, ALT 31 - LO MARCOLETA -</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>QUILICURA</t>
+  </si>
+  <si>
+    <t>LO MARCOLETA</t>
+  </si>
+  <si>
+    <t>965115499</t>
+  </si>
+  <si>
+    <t>D4075473@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>Planes Parque</t>
+  </si>
+  <si>
+    <t>Valle De La Memoria (cuotas)</t>
+  </si>
+  <si>
+    <t>Valle De La Memoria</t>
+  </si>
+  <si>
+    <t>4990000</t>
+  </si>
+  <si>
+    <t>2986395</t>
+  </si>
+  <si>
+    <t>59.85</t>
+  </si>
+  <si>
+    <t>2003605</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>3-AJ-41</t>
+  </si>
+  <si>
+    <t>Valle de la Memoria</t>
+  </si>
+  <si>
+    <t>2023-07-31T00:00:00</t>
+  </si>
+  <si>
+    <t>1015781</t>
+  </si>
+  <si>
+    <t>105451</t>
   </si>
   <si>
     <t>1015755</t>
   </si>
   <si>
-    <t>82920</t>
-  </si>
-  <si>
-    <t>NF CARTERA</t>
-  </si>
-  <si>
     <t>07/04/2026</t>
   </si>
   <si>
@@ -262,24 +518,6 @@
     <t>yvanaparada71@gmail.com</t>
   </si>
   <si>
-    <t>Planes Parque</t>
-  </si>
-  <si>
-    <t>Valle De La Memoria (cuotas)</t>
-  </si>
-  <si>
-    <t>Valle De La Memoria</t>
-  </si>
-  <si>
-    <t>4990000</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>3000000</t>
-  </si>
-  <si>
     <t>60.12</t>
   </si>
   <si>
@@ -295,22 +533,274 @@
     <t>07/05/2026</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>3-AM-25</t>
   </si>
   <si>
-    <t>Valle de la Memoria</t>
-  </si>
-  <si>
     <t>2026-03-26T00:00:00</t>
   </si>
   <si>
+    <t>1015782</t>
+  </si>
+  <si>
+    <t>350000</t>
+  </si>
+  <si>
+    <t>MUÑOZ PEÑA CLAUDIO GREGORIO</t>
+  </si>
+  <si>
+    <t>12834568-K</t>
+  </si>
+  <si>
+    <t>RIO MAULE 2750 CASA 85, ALT 85 - VALLE GRANDE -</t>
+  </si>
+  <si>
+    <t>LAMPA</t>
+  </si>
+  <si>
+    <t>VALLE GRANDE</t>
+  </si>
+  <si>
+    <t>974526722</t>
+  </si>
+  <si>
+    <t>4220000</t>
+  </si>
+  <si>
+    <t>84.57</t>
+  </si>
+  <si>
+    <t>770000</t>
+  </si>
+  <si>
+    <t>154000</t>
+  </si>
+  <si>
+    <t>3-M-24</t>
+  </si>
+  <si>
+    <t>2026-04-09T00:00:00</t>
+  </si>
+  <si>
+    <t>1015786</t>
+  </si>
+  <si>
+    <t>1360000</t>
+  </si>
+  <si>
+    <t>Fernanda Scarlet Cuevas Olivares</t>
+  </si>
+  <si>
+    <t>CARVAJAL SAGREDO RAFAEL IGNACIO</t>
+  </si>
+  <si>
+    <t>9867041-6</t>
+  </si>
+  <si>
+    <t>Las pablonias, ALT 1485 - Quilicura -</t>
+  </si>
+  <si>
+    <t>966273118</t>
+  </si>
+  <si>
+    <t>rafael.sagredo@gmail.com</t>
+  </si>
+  <si>
+    <t>Planes Descanso de Cenizas</t>
+  </si>
+  <si>
+    <t>Destellos De Luz</t>
+  </si>
+  <si>
+    <t>Destellos de Luz</t>
+  </si>
+  <si>
+    <t>1700000</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>340000</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>14/05/2026</t>
+  </si>
+  <si>
+    <t>SIN ASIGNAR</t>
+  </si>
+  <si>
+    <t>MIGRAR</t>
+  </si>
+  <si>
+    <t>2026-04-14T00:00:00</t>
+  </si>
+  <si>
+    <t>1015758</t>
+  </si>
+  <si>
+    <t>ERNESTO OLIVA</t>
+  </si>
+  <si>
+    <t>MIGUEL SANDOVAL</t>
+  </si>
+  <si>
+    <t>ANDREA CONCHA ADASME</t>
+  </si>
+  <si>
+    <t>MUÑOZ FLORES MANUEL  ALEJANDRO</t>
+  </si>
+  <si>
+    <t>12112040-3</t>
+  </si>
+  <si>
+    <t>Las petunias  540, Quilicura, Santiago, Metropolitana  Casa:</t>
+  </si>
+  <si>
+    <t>921609666</t>
+  </si>
+  <si>
+    <t>martha.moontero@hotmail.com</t>
+  </si>
+  <si>
+    <t>500000</t>
+  </si>
+  <si>
+    <t>499000</t>
+  </si>
+  <si>
+    <t>4491000</t>
+  </si>
+  <si>
+    <t>3991000</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>66497</t>
+  </si>
+  <si>
+    <t>3-BD-34</t>
+  </si>
+  <si>
+    <t>1015735</t>
+  </si>
+  <si>
+    <t>LIDIA MONICA FLORES BRAVO</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>ROBLES CISTERNAS MARGARITA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>12353329-1</t>
+  </si>
+  <si>
+    <t>El medio dia, ALT 358 - Quilicura -</t>
+  </si>
+  <si>
+    <t>994485350</t>
+  </si>
+  <si>
+    <t>robles.cisterm@gmail.com</t>
+  </si>
+  <si>
+    <t>4490000</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>76084</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>3-V-21</t>
+  </si>
+  <si>
+    <t>1015750</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>SANCHEZ MATUS ISAAC  ESTEBAN</t>
+  </si>
+  <si>
+    <t>17517932-1</t>
+  </si>
+  <si>
+    <t>Blanco encalada  102, Quilicura, Santiago, Metropolitana  Pi/dp Casa E Casa:</t>
+  </si>
+  <si>
+    <t>984602304</t>
+  </si>
+  <si>
+    <t>930860950</t>
+  </si>
+  <si>
+    <t>aylenyanto23@gmail.com</t>
+  </si>
+  <si>
+    <t>4-A-27</t>
+  </si>
+  <si>
+    <t>Valle de la Memoria 2</t>
+  </si>
+  <si>
+    <t>1015748</t>
+  </si>
+  <si>
+    <t>Estefany francisca gonzalez morales</t>
+  </si>
+  <si>
+    <t>YASMELY RAMONA VARGAS INFANTE</t>
+  </si>
+  <si>
+    <t>VARGAS CAMPOS LUIS MIGUEL</t>
+  </si>
+  <si>
+    <t>12003266-6</t>
+  </si>
+  <si>
+    <t>Blanco Encalada, ALT 144 - Quilicura -</t>
+  </si>
+  <si>
+    <t>931377299</t>
+  </si>
+  <si>
+    <t>LUISMIGUEL.VARGASC@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>450000</t>
+  </si>
+  <si>
+    <t>4041000</t>
+  </si>
+  <si>
+    <t>112250</t>
+  </si>
+  <si>
+    <t>4-O-25</t>
+  </si>
+  <si>
     <t>1015757</t>
   </si>
   <si>
-    <t>350000</t>
+    <t>13/04/2026</t>
   </si>
   <si>
     <t>VARGAS AGUIRRE CARLOS ANTONIO</t>
@@ -322,12 +812,6 @@
     <t>PUCON 409, ALT 409 - Quilicura -</t>
   </si>
   <si>
-    <t>Santiago</t>
-  </si>
-  <si>
-    <t>Quilicura</t>
-  </si>
-  <si>
     <t>985674375</t>
   </si>
   <si>
@@ -346,10 +830,7 @@
     <t>3445000</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>57416.66</t>
+    <t>57397</t>
   </si>
   <si>
     <t>30</t>
@@ -361,247 +842,7 @@
     <t>4-Z-39</t>
   </si>
   <si>
-    <t>Valle de la Memoria 2</t>
-  </si>
-  <si>
     <t>2026-04-01T00:00:00</t>
-  </si>
-  <si>
-    <t>1015752</t>
-  </si>
-  <si>
-    <t>ABONADO</t>
-  </si>
-  <si>
-    <t>300000</t>
-  </si>
-  <si>
-    <t>Rodrigo Ignacio Castro Figueroa</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ BARRIOS MARTA ORIANA</t>
-  </si>
-  <si>
-    <t>7078549-8</t>
-  </si>
-  <si>
-    <t>Psj ventana, ALT 521 - Quilicura -</t>
-  </si>
-  <si>
-    <t>987185292</t>
-  </si>
-  <si>
-    <t>223515177</t>
-  </si>
-  <si>
-    <t>martadominguezbarrios@gmail.com</t>
-  </si>
-  <si>
-    <t>Mantención Perpetua Integral</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>2700000</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>75000</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20/05/2026</t>
-  </si>
-  <si>
-    <t>2026-04-06T00:00:00</t>
-  </si>
-  <si>
-    <t>1015739</t>
-  </si>
-  <si>
-    <t>Marcela Antonia  Valdés  Barrios</t>
-  </si>
-  <si>
-    <t>ALVARADO ORTIZ ORTIZ JACQUELINE DEL CARMEN</t>
-  </si>
-  <si>
-    <t>9765730-0</t>
-  </si>
-  <si>
-    <t>ALFREDO SANTANDER, ALT 1539 - Quilicura -</t>
-  </si>
-  <si>
-    <t>988574499</t>
-  </si>
-  <si>
-    <t>jacquelinealvarado356@gmail.com</t>
-  </si>
-  <si>
-    <t>112500</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>2026-04-07T00:00:00</t>
-  </si>
-  <si>
-    <t>1015758</t>
-  </si>
-  <si>
-    <t>500000</t>
-  </si>
-  <si>
-    <t>ERNESTO OLIVA</t>
-  </si>
-  <si>
-    <t>MIGUEL SANDOVAL</t>
-  </si>
-  <si>
-    <t>ANDREA CONCHA ADASME</t>
-  </si>
-  <si>
-    <t>MUÑOZ FLORES MANUEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>12.112.040-3</t>
-  </si>
-  <si>
-    <t>Las petunias , ALT 540 - Quilicura -</t>
-  </si>
-  <si>
-    <t>921609666</t>
-  </si>
-  <si>
-    <t>martha.moontero@hotmail.com</t>
-  </si>
-  <si>
-    <t>499000</t>
-  </si>
-  <si>
-    <t>4491000</t>
-  </si>
-  <si>
-    <t>3991000</t>
-  </si>
-  <si>
-    <t>66516.66</t>
-  </si>
-  <si>
-    <t>3-BD-34</t>
-  </si>
-  <si>
-    <t>1015735</t>
-  </si>
-  <si>
-    <t>GABRIELA DEL CARMEN ROJAS QUEZADA</t>
-  </si>
-  <si>
-    <t>LIDIA MONICA FLORES BRAVO</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>ROBLES CISTERNAS MARGARITA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>12353329-1</t>
-  </si>
-  <si>
-    <t>El medio dia, ALT 358 - Quilicura -</t>
-  </si>
-  <si>
-    <t>994485350</t>
-  </si>
-  <si>
-    <t>robles.cisterm@gmail.com</t>
-  </si>
-  <si>
-    <t>4490000</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>76084</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>15/05/2026</t>
-  </si>
-  <si>
-    <t>3-V-21</t>
-  </si>
-  <si>
-    <t>1015750</t>
-  </si>
-  <si>
-    <t>SANCHEZ MATUS ISAAC  ESTEBAN</t>
-  </si>
-  <si>
-    <t>17517932-1</t>
-  </si>
-  <si>
-    <t>Blanco encalada  102, Quilicura, Santiago, Metropolitana  Pi/dp Casa E Casa:</t>
-  </si>
-  <si>
-    <t>984602304</t>
-  </si>
-  <si>
-    <t>930860950</t>
-  </si>
-  <si>
-    <t>aylenyanto23@gmail.com</t>
-  </si>
-  <si>
-    <t>4-A-27</t>
-  </si>
-  <si>
-    <t>1015748</t>
-  </si>
-  <si>
-    <t>Estefany francisca gonzalez morales</t>
-  </si>
-  <si>
-    <t>YASMELY RAMONA VARGAS INFANTE</t>
-  </si>
-  <si>
-    <t>VARGAS CAMPOS LUIS MIGUEL</t>
-  </si>
-  <si>
-    <t>12003266-6</t>
-  </si>
-  <si>
-    <t>Blanco Encalada, ALT 144 - Quilicura -</t>
-  </si>
-  <si>
-    <t>931377299</t>
-  </si>
-  <si>
-    <t>LUISMIGUEL.VARGASC@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>450000</t>
-  </si>
-  <si>
-    <t>4041000</t>
-  </si>
-  <si>
-    <t>112250</t>
-  </si>
-  <si>
-    <t>4-O-25</t>
   </si>
   <si>
     <t>1015754</t>
@@ -1522,11 +1763,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM11"/>
+  <dimension ref="A1:AM17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="38" width="8" customWidth="1"/>
-    <col min="39" max="39" width="15" customWidth="1"/>
+    <col min="1" max="39" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.3">
@@ -1775,115 +2015,115 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
         <v>73</v>
       </c>
       <c r="I3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" t="s">
         <v>74</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>75</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>76</v>
-      </c>
-      <c r="L3" t="s">
-        <v>77</v>
       </c>
       <c r="M3" t="s">
         <v>50</v>
       </c>
       <c r="N3" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="O3" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S3" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="T3" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="U3" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="V3" t="s">
         <v>56</v>
       </c>
       <c r="W3" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="X3" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="Y3" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="Z3" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="AB3" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="AC3" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="AD3" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="AE3" t="s">
         <v>65</v>
       </c>
       <c r="AF3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="AG3" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="AH3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="AJ3" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="AK3" t="s">
-        <v>92</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.3">
@@ -1891,118 +2131,118 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="I4" t="s">
         <v>44</v>
       </c>
       <c r="J4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s">
         <v>50</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="O4" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="P4" t="s">
-        <v>102</v>
+        <v>44</v>
       </c>
       <c r="Q4" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="R4" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="S4" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="T4" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="U4" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="V4" t="s">
         <v>56</v>
       </c>
       <c r="W4" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="X4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="Y4" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="Z4" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="AA4" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="AB4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="AC4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="AE4" t="s">
         <v>65</v>
       </c>
       <c r="AF4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AH4" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="AI4" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="AJ4" t="s">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="AK4" t="s">
-        <v>112</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="s">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.3">
@@ -2010,13 +2250,13 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>43</v>
@@ -2028,88 +2268,88 @@
         <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I5" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="J5" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K5" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="L5" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="M5" t="s">
         <v>50</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="O5" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="P5" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="Q5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="R5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="S5" t="s">
         <v>44</v>
       </c>
       <c r="T5" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="U5" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="V5" t="s">
         <v>56</v>
       </c>
       <c r="W5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="X5" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="Y5" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="Z5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="AA5" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="AB5" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AC5" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="AD5" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="AE5" t="s">
         <v>65</v>
       </c>
       <c r="AF5" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="AG5" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="AH5" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="AI5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="AJ5" t="s">
         <v>44</v>
@@ -2121,7 +2361,7 @@
         <v>44</v>
       </c>
       <c r="AM5" t="s">
-        <v>132</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.3">
@@ -2129,13 +2369,13 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>43</v>
@@ -2147,88 +2387,88 @@
         <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="J6" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="K6" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="L6" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="M6" t="s">
         <v>50</v>
       </c>
       <c r="N6" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="O6" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="P6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="Q6" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="R6" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="S6" t="s">
         <v>44</v>
       </c>
       <c r="T6" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="U6" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="V6" t="s">
         <v>56</v>
       </c>
       <c r="W6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="X6" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="Y6" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="Z6" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="AA6" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="AB6" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AC6" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="AD6" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="AE6" t="s">
         <v>65</v>
       </c>
       <c r="AF6" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="AG6" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="AH6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="AI6" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="AJ6" t="s">
         <v>44</v>
@@ -2240,7 +2480,7 @@
         <v>44</v>
       </c>
       <c r="AM6" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.3">
@@ -2248,118 +2488,118 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I7" t="s">
         <v>44</v>
       </c>
       <c r="J7" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="K7" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="L7" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="M7" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="O7" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="P7" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="Q7" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="R7" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="S7" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="T7" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="U7" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="V7" t="s">
         <v>56</v>
       </c>
       <c r="W7" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="X7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA7" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>154</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>61</v>
-      </c>
       <c r="AB7" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="AC7" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="AD7" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="AE7" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AF7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="AH7" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="AI7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="AJ7" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="AK7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="AL7" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="AM7" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.3">
@@ -2367,118 +2607,118 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>84</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
         <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>160</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="I8" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="K8" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="L8" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="O8" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="P8" t="s">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="Q8" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="R8" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="S8" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="T8" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="U8" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="V8" t="s">
         <v>56</v>
       </c>
       <c r="W8" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="X8" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA8" t="s">
         <v>145</v>
       </c>
-      <c r="Y8" t="s">
-        <v>126</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>84</v>
-      </c>
       <c r="AB8" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="AC8" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="AD8" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="AE8" t="s">
         <v>65</v>
       </c>
       <c r="AF8" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="AG8" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="AH8" t="s">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="AI8" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="AJ8" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="AK8" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="AL8" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="AM8" t="s">
-        <v>44</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.3">
@@ -2486,118 +2726,118 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>155</v>
       </c>
       <c r="J9" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="K9" t="s">
-        <v>176</v>
+        <v>157</v>
       </c>
       <c r="L9" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="M9" t="s">
         <v>50</v>
       </c>
       <c r="N9" t="s">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="P9" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="Q9" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="R9" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="S9" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="T9" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="U9" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="V9" t="s">
         <v>56</v>
       </c>
       <c r="W9" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="X9" t="s">
-        <v>145</v>
+        <v>98</v>
       </c>
       <c r="Y9" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="Z9" t="s">
-        <v>154</v>
+        <v>96</v>
       </c>
       <c r="AA9" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="AB9" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AC9" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AD9" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="AE9" t="s">
         <v>65</v>
       </c>
       <c r="AF9" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="AG9" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="AH9" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="AI9" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="AJ9" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="AK9" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="AL9" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="AM9" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.3">
@@ -2605,118 +2845,118 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
         <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="I10" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="J10" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="K10" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="L10" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="M10" t="s">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s">
-        <v>100</v>
+        <v>173</v>
       </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>174</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="Q10" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="R10" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="S10" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="T10" t="s">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="U10" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="V10" t="s">
         <v>56</v>
       </c>
       <c r="W10" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="X10" t="s">
-        <v>190</v>
+        <v>98</v>
       </c>
       <c r="Y10" t="s">
-        <v>59</v>
+        <v>98</v>
       </c>
       <c r="Z10" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="AA10" t="s">
-        <v>61</v>
+        <v>177</v>
       </c>
       <c r="AB10" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="AC10" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="AD10" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="AE10" t="s">
         <v>65</v>
       </c>
       <c r="AF10" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="AG10" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="AH10" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="AI10" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="AJ10" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="AK10" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="AL10" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="AM10" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.3">
@@ -2724,13 +2964,13 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="E11" t="s">
         <v>43</v>
@@ -2739,102 +2979,816 @@
         <v>44</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="I11" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="J11" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="K11" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="L11" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="M11" t="s">
         <v>50</v>
       </c>
       <c r="N11" t="s">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="O11" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
       <c r="Q11" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="R11" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="S11" t="s">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="T11" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="U11" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="V11" t="s">
         <v>56</v>
       </c>
       <c r="W11" t="s">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="X11" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="Y11" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="Z11" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="AA11" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="AB11" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AC11" t="s">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="AD11" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="AE11" t="s">
         <v>65</v>
       </c>
       <c r="AF11" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>197</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>200</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" t="s">
+        <v>203</v>
+      </c>
+      <c r="G12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H12" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" t="s">
+        <v>206</v>
+      </c>
+      <c r="K12" t="s">
+        <v>207</v>
+      </c>
+      <c r="L12" t="s">
+        <v>208</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" t="s">
+        <v>77</v>
+      </c>
+      <c r="O12" t="s">
+        <v>78</v>
+      </c>
+      <c r="P12" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q12" t="s">
         <v>209</v>
       </c>
-      <c r="AG11" t="s">
+      <c r="R12" t="s">
         <v>210</v>
       </c>
-      <c r="AH11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI11" t="s">
+      <c r="S12" t="s">
+        <v>140</v>
+      </c>
+      <c r="T12" t="s">
+        <v>141</v>
+      </c>
+      <c r="U12" t="s">
+        <v>142</v>
+      </c>
+      <c r="V12" t="s">
+        <v>56</v>
+      </c>
+      <c r="W12" t="s">
+        <v>143</v>
+      </c>
+      <c r="X12" t="s">
         <v>211</v>
       </c>
-      <c r="AJ11" t="s">
-        <v>91</v>
-      </c>
-      <c r="AK11" t="s">
+      <c r="Y12" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z12" t="s">
         <v>212</v>
       </c>
-      <c r="AL11" t="s">
+      <c r="AA12" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB12" t="s">
         <v>213</v>
       </c>
-      <c r="AM11" t="s">
+      <c r="AC12" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>165</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>217</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" t="s">
+        <v>219</v>
+      </c>
+      <c r="I13" t="s">
+        <v>220</v>
+      </c>
+      <c r="J13" t="s">
+        <v>221</v>
+      </c>
+      <c r="K13" t="s">
+        <v>222</v>
+      </c>
+      <c r="L13" t="s">
+        <v>223</v>
+      </c>
+      <c r="M13" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
+      </c>
+      <c r="O13" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>224</v>
+      </c>
+      <c r="R13" t="s">
+        <v>225</v>
+      </c>
+      <c r="S13" t="s">
+        <v>140</v>
+      </c>
+      <c r="T13" t="s">
+        <v>141</v>
+      </c>
+      <c r="U13" t="s">
+        <v>142</v>
+      </c>
+      <c r="V13" t="s">
+        <v>56</v>
+      </c>
+      <c r="W13" t="s">
+        <v>143</v>
+      </c>
+      <c r="X13" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>226</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>228</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>229</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>230</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F14" t="s">
+        <v>203</v>
+      </c>
+      <c r="G14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" t="s">
+        <v>205</v>
+      </c>
+      <c r="I14" t="s">
+        <v>233</v>
+      </c>
+      <c r="J14" t="s">
+        <v>234</v>
+      </c>
+      <c r="K14" t="s">
+        <v>235</v>
+      </c>
+      <c r="L14" t="s">
+        <v>236</v>
+      </c>
+      <c r="M14" t="s">
+        <v>50</v>
+      </c>
+      <c r="N14" t="s">
+        <v>77</v>
+      </c>
+      <c r="O14" t="s">
+        <v>78</v>
+      </c>
+      <c r="P14" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>238</v>
+      </c>
+      <c r="R14" t="s">
+        <v>239</v>
+      </c>
+      <c r="S14" t="s">
+        <v>140</v>
+      </c>
+      <c r="T14" t="s">
+        <v>141</v>
+      </c>
+      <c r="U14" t="s">
+        <v>142</v>
+      </c>
+      <c r="V14" t="s">
+        <v>56</v>
+      </c>
+      <c r="W14" t="s">
+        <v>143</v>
+      </c>
+      <c r="X14" t="s">
+        <v>211</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>216</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>68</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>69</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" t="s">
+        <v>98</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" t="s">
+        <v>243</v>
+      </c>
+      <c r="H15" t="s">
+        <v>244</v>
+      </c>
+      <c r="I15" t="s">
+        <v>155</v>
+      </c>
+      <c r="J15" t="s">
+        <v>245</v>
+      </c>
+      <c r="K15" t="s">
+        <v>246</v>
+      </c>
+      <c r="L15" t="s">
+        <v>247</v>
+      </c>
+      <c r="M15" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" t="s">
+        <v>77</v>
+      </c>
+      <c r="O15" t="s">
+        <v>78</v>
+      </c>
+      <c r="P15" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>248</v>
+      </c>
+      <c r="R15" t="s">
+        <v>249</v>
+      </c>
+      <c r="S15" t="s">
+        <v>140</v>
+      </c>
+      <c r="T15" t="s">
+        <v>141</v>
+      </c>
+      <c r="U15" t="s">
+        <v>142</v>
+      </c>
+      <c r="V15" t="s">
+        <v>56</v>
+      </c>
+      <c r="W15" t="s">
+        <v>143</v>
+      </c>
+      <c r="X15" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>251</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>125</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>252</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AI15" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>253</v>
+      </c>
+      <c r="AL15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
+        <v>169</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" t="s">
+        <v>255</v>
+      </c>
+      <c r="J16" t="s">
+        <v>256</v>
+      </c>
+      <c r="K16" t="s">
+        <v>257</v>
+      </c>
+      <c r="L16" t="s">
+        <v>258</v>
+      </c>
+      <c r="M16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" t="s">
+        <v>77</v>
+      </c>
+      <c r="O16" t="s">
+        <v>78</v>
+      </c>
+      <c r="P16" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>260</v>
+      </c>
+      <c r="R16" t="s">
+        <v>261</v>
+      </c>
+      <c r="S16" t="s">
+        <v>140</v>
+      </c>
+      <c r="T16" t="s">
+        <v>141</v>
+      </c>
+      <c r="U16" t="s">
+        <v>142</v>
+      </c>
+      <c r="V16" t="s">
+        <v>56</v>
+      </c>
+      <c r="W16" t="s">
+        <v>143</v>
+      </c>
+      <c r="X16" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>262</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>263</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>264</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>264</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>264</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>215</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>266</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>267</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>268</v>
+      </c>
+      <c r="AL16" t="s">
+        <v>241</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
+        <v>270</v>
+      </c>
+      <c r="C17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>243</v>
+      </c>
+      <c r="H17" t="s">
+        <v>271</v>
+      </c>
+      <c r="I17" t="s">
+        <v>155</v>
+      </c>
+      <c r="J17" t="s">
+        <v>272</v>
+      </c>
+      <c r="K17" t="s">
+        <v>273</v>
+      </c>
+      <c r="L17" t="s">
+        <v>274</v>
+      </c>
+      <c r="M17" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" t="s">
+        <v>275</v>
+      </c>
+      <c r="O17" t="s">
+        <v>276</v>
+      </c>
+      <c r="P17" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>278</v>
+      </c>
+      <c r="R17" t="s">
+        <v>279</v>
+      </c>
+      <c r="S17" t="s">
+        <v>140</v>
+      </c>
+      <c r="T17" t="s">
+        <v>280</v>
+      </c>
+      <c r="U17" t="s">
+        <v>281</v>
+      </c>
+      <c r="V17" t="s">
+        <v>56</v>
+      </c>
+      <c r="W17" t="s">
+        <v>143</v>
+      </c>
+      <c r="X17" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>283</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>143</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>284</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>285</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>286</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>148</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>287</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>288</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>289</v>
+      </c>
+      <c r="AM17" t="s">
         <v>44</v>
       </c>
     </row>
